--- a/All_2026.xlsx
+++ b/All_2026.xlsx
@@ -9,7 +9,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fetonline-my.sharepoint.com/personal/jasonh5_fareastone_com_tw/Documents/桌面/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:10000_{477BEA85-29B0-4080-8B8D-7C658BF4DB82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:10000_{9CD085C7-403F-4D39-ADF0-5F4F02F4D9EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{F48F8574-E72E-47A9-9FAE-C071219C9035}"/>
   </bookViews>
@@ -14628,7 +14628,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>排休</t>
         </r>
@@ -14637,7 +14637,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -14651,7 +14651,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">N
 </t>
@@ -14681,7 +14681,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>N</t>
         </r>
@@ -14695,7 +14695,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>排休</t>
         </r>
@@ -14704,7 +14704,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -16042,7 +16042,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>遠傳新春展望全競會</t>
         </r>
@@ -16051,7 +16051,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -16140,7 +16140,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>遠傳新春展望全競會</t>
         </r>
@@ -16149,7 +16149,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -18938,7 +18938,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">回診
 </t>
@@ -18952,7 +18952,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">回診
 </t>
@@ -18967,7 +18967,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>小夜大夜或休假</t>
         </r>
@@ -18976,7 +18976,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -18991,7 +18991,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>排休</t>
         </r>
@@ -19005,7 +19005,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>小夜大夜或休假</t>
         </r>
@@ -19014,7 +19014,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -19029,7 +19029,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>小夜大夜或休假</t>
         </r>
@@ -19038,7 +19038,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -19053,7 +19053,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>小夜大夜或休假</t>
         </r>
@@ -19062,7 +19062,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -19990,7 +19990,7 @@
     <numFmt numFmtId="165" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="166" formatCode="0_ "/>
   </numFmts>
-  <fonts count="100">
+  <fonts count="98">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -20650,19 +20650,6 @@
       <name val="細明體"/>
       <family val="3"/>
       <charset val="136"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
@@ -22207,83 +22194,74 @@
     <xf numFmtId="165" fontId="23" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="5" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="5" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="10" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="12" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="10" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="12" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="12" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="8" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="12" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="8" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="6" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="97" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -22291,16 +22269,25 @@
     <xf numFmtId="0" fontId="97" fillId="6" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="8" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="6" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="6" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="98" fillId="6" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="8" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="6" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="6" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="10" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -22315,22 +22302,22 @@
     <xf numFmtId="0" fontId="22" fillId="7" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="8" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="8" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="5" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="5" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -22345,22 +22332,22 @@
     <xf numFmtId="0" fontId="31" fillId="9" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="19" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="19" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="5" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="5" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="6" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="6" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="19" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="19" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="19" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="19" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="19" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="19" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22441,6 +22428,31 @@
     <cellStyle name="一般 2" xfId="1" xr:uid="{49B4DAFB-6DB6-4F0B-A98F-E68CAA2AC64E}"/>
   </cellStyles>
   <dxfs count="84">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -22569,31 +22581,6 @@
           <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -52764,7 +52751,7 @@
       <c r="J1" s="4"/>
       <c r="K1" s="296" t="str">
         <f>"TPKC剩餘人力："&amp;AR58&amp;" / NK剩餘人力："&amp;AS58&amp;" /  N班人力："&amp;AR53</f>
-        <v>TPKC剩餘人力：-1 / NK剩餘人力：0 /  N班人力：114</v>
+        <v>TPKC剩餘人力：-1 / NK剩餘人力：0 /  N班人力：112</v>
       </c>
       <c r="L1" s="297"/>
       <c r="M1" s="297"/>
@@ -56559,7 +56546,7 @@
     <row r="17" spans="1:226" ht="25.2" customHeight="1">
       <c r="A17" s="54">
         <f>COUNTIF(K17:AO17,1)+COUNTIF(K17:AO17,"早")+COUNTIF(K17:AO17,"M1")+COUNTIF(K17:AO17,"T早")+COUNTIF(K17:AO17,"日")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B17" s="55">
         <f>COUNTIF(K17:AO17,2)+COUNTIF(K17:AO17,"中")+COUNTIF(K17:AO17,"M2")+COUNTIF(K17:AO17,"T中")+COUNTIF(K17:AO17,"小夜")</f>
@@ -56571,7 +56558,7 @@
       </c>
       <c r="D17" s="55">
         <f>COUNTIF(K17:AO17,"N")+COUNTIF(K17:AO17,"N8")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="17">
         <f>COUNTIF(K17:AO17,"S")</f>
@@ -56665,8 +56652,8 @@
       <c r="AG17" s="234" t="s">
         <v>1</v>
       </c>
-      <c r="AH17" s="238" t="s">
-        <v>3</v>
+      <c r="AH17" s="238">
+        <v>1</v>
       </c>
       <c r="AI17" s="238">
         <v>1</v>
@@ -56721,7 +56708,7 @@
     <row r="18" spans="1:226" ht="25.5" customHeight="1" thickBot="1">
       <c r="A18" s="38">
         <f t="shared" ref="A18" si="12">COUNTIF(K18:AO18,1)+COUNTIF(K18:AO18,"早")+COUNTIF(K18:AO18,"M1")+COUNTIF(K18:AO18,"T早")+COUNTIF(K18:AO18,"日")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" s="39">
         <f t="shared" ref="B18" si="13">COUNTIF(K18:AO18,2)+COUNTIF(K18:AO18,"中")+COUNTIF(K18:AO18,"M2")+COUNTIF(K18:AO18,"T中")+COUNTIF(K18:AO18,"小夜")</f>
@@ -56733,7 +56720,7 @@
       </c>
       <c r="D18" s="39">
         <f t="shared" ref="D18" si="15">COUNTIF(K18:AO18,"N")+COUNTIF(K18:AO18,"N8")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="41">
         <f t="shared" ref="E18" si="16">COUNTIF(K18:AO18,"S")</f>
@@ -56824,8 +56811,8 @@
       <c r="AF18" s="263">
         <v>1</v>
       </c>
-      <c r="AG18" s="248" t="s">
-        <v>3</v>
+      <c r="AG18" s="238">
+        <v>1</v>
       </c>
       <c r="AH18" s="60" t="s">
         <v>36</v>
@@ -59169,7 +59156,7 @@
     <row r="27" spans="1:226" s="50" customFormat="1" ht="25.5" customHeight="1">
       <c r="A27" s="38">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B27" s="39">
         <f t="shared" si="3"/>
@@ -59185,7 +59172,7 @@
       </c>
       <c r="E27" s="41">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27" s="41">
         <f t="shared" si="7"/>
@@ -59272,10 +59259,10 @@
       <c r="AF27" s="239" t="s">
         <v>0</v>
       </c>
-      <c r="AG27" s="238">
-        <v>1</v>
-      </c>
-      <c r="AH27" s="238">
+      <c r="AG27" s="234" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH27" s="234" t="s">
         <v>1</v>
       </c>
       <c r="AI27" s="238" t="s">
@@ -66246,7 +66233,7 @@
       </c>
       <c r="AR53" s="91" cm="1">
         <f t="array" ref="AR53">SUMPRODUCT(COUNTIF(K4:AO40,{"N";"N8"}))</f>
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AS53" s="91" cm="1">
         <f t="array" ref="AS53">SUMPRODUCT(COUNTIF(K41:AO46,{"N";"N8"}))</f>
@@ -66392,7 +66379,7 @@
       </c>
       <c r="AR54" s="92">
         <f>SUMPRODUCT(COUNTIF(K4:AO40,{"S"}))</f>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AS54" s="75">
         <f>SUMPRODUCT(COUNTIF(K41:AO46,{"S"}))</f>
@@ -66643,11 +66630,11 @@
       </c>
       <c r="AG56" s="96">
         <f t="shared" si="51"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH56" s="96">
         <f t="shared" si="51"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI56" s="96">
         <f t="shared" si="51"/>
@@ -66932,11 +66919,11 @@
       </c>
       <c r="AG58" s="39">
         <f t="shared" si="55"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH58" s="39">
         <f t="shared" si="55"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI58" s="39">
         <f t="shared" si="55"/>
@@ -67566,11 +67553,11 @@
       </c>
       <c r="AG64" s="230" cm="1">
         <f t="array" ref="AG64">SUMPRODUCT(COUNTIF(AG4:AG18,{"1";"M1"}))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH64" s="230" cm="1">
         <f t="array" ref="AH64">SUMPRODUCT(COUNTIF(AH4:AH18,{"1";"M1"}))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI64" s="230" cm="1">
         <f t="array" ref="AI64">SUMPRODUCT(COUNTIF(AI4:AI18,{"1";"M1"}))</f>
@@ -67629,87 +67616,87 @@
     <mergeCell ref="E2:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="K4:AO46">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>OR(K4=3, K4="晚",  K4="大夜")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>OR(K4="M2", K4=2, K4="中", K4="T中", K4="小夜")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>OR(K4="M1", K4=1, K4="早", K4="T早", K4="日")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="4">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>OR(     SUM(COUNTIF(K4:Q4, 上班代號)) &gt; 6,     AND(COLUMN()&gt;11, OR(         AND(SUM(COUNTIF(OFFSET(K4,0,-1), 中班組)), SUM(COUNTIF(K4, 早班組), COUNTIF(K4, 晚班組))),         AND(SUM(COUNTIF(OFFSET(K4,0,-1), 早班組)), SUM(COUNTIF(K4, 晚班組)))     )) )</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K47:AO55">
-    <cfRule type="cellIs" dxfId="20" priority="202" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="202" operator="equal">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="203" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="203" operator="equal">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="204" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="204" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="205" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="205" operator="equal">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="206" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="206" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K53:AO55">
-    <cfRule type="cellIs" dxfId="15" priority="207" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="207" operator="equal">
       <formula>"T中"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP25">
-    <cfRule type="cellIs" dxfId="14" priority="210" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="210" operator="equal">
       <formula>"大夜"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="211" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="211" operator="equal">
       <formula>"晚"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="212" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="212" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="213" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="213" operator="equal">
       <formula>"小夜"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="214" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="214" operator="equal">
       <formula>"T中"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="215" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="215" operator="equal">
       <formula>"中"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="216" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="216" operator="equal">
       <formula>"M2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="217" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="217" operator="equal">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="218" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="218" operator="equal">
       <formula>"日"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="219" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="219" operator="equal">
       <formula>"T早"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="220" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="220" operator="equal">
       <formula>"早"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="221" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="221" operator="equal">
       <formula>"M1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="222" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="222" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS4:AS46">
-    <cfRule type="cellIs" dxfId="1" priority="208" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="208" operator="equal">
       <formula>-2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="209" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="209" operator="equal">
       <formula>-1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/All_2026.xlsx
+++ b/All_2026.xlsx
@@ -9,7 +9,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fetonline-my.sharepoint.com/personal/jasonh5_fareastone_com_tw/Documents/桌面/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:10000_{9CD085C7-403F-4D39-ADF0-5F4F02F4D9EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:10000_{0B63F5BA-DE81-4C73-AF12-8D588C21A7C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{F48F8574-E72E-47A9-9FAE-C071219C9035}"/>
   </bookViews>
@@ -13650,27 +13650,18 @@
         </r>
       </text>
     </comment>
-    <comment ref="L10" authorId="1" shapeId="0" xr:uid="{AB2E4D04-40E9-4176-8F38-1ECF44C3A7CE}">
+    <comment ref="L10" authorId="1" shapeId="0" xr:uid="{B4899455-2B0D-4EED-96A7-E553B68D23E8}">
       <text>
         <r>
           <rPr>
             <b/>
-            <sz val="9"/>
+            <sz val="11"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>過年補假</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
+          <t>過年補假
+申報加班</t>
         </r>
       </text>
     </comment>
@@ -19360,7 +19351,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3485" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3484" uniqueCount="153">
   <si>
     <t>X</t>
   </si>
@@ -21496,7 +21487,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="309">
+  <cellXfs count="308">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -22350,9 +22341,6 @@
     <xf numFmtId="0" fontId="95" fillId="19" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -22428,31 +22416,6 @@
     <cellStyle name="一般 2" xfId="1" xr:uid="{49B4DAFB-6DB6-4F0B-A98F-E68CAA2AC64E}"/>
   </cellStyles>
   <dxfs count="84">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -22581,6 +22544,31 @@
           <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -23304,57 +23292,57 @@
         <v>10</v>
       </c>
       <c r="J1" s="4"/>
-      <c r="K1" s="296" t="str">
+      <c r="K1" s="295" t="str">
         <f>"TPKC剩餘人力："&amp;AR59&amp;" / NK剩餘人力："&amp;AS59&amp;" /  N班人力："&amp;AR53</f>
         <v>TPKC剩餘人力：0 / NK剩餘人力：0 /  N班人力：92</v>
       </c>
-      <c r="L1" s="297"/>
-      <c r="M1" s="297"/>
-      <c r="N1" s="297"/>
-      <c r="O1" s="297"/>
-      <c r="P1" s="297"/>
-      <c r="Q1" s="297"/>
-      <c r="R1" s="297"/>
-      <c r="S1" s="297"/>
-      <c r="T1" s="297"/>
-      <c r="U1" s="297"/>
-      <c r="V1" s="297"/>
-      <c r="W1" s="297"/>
-      <c r="X1" s="297"/>
-      <c r="Y1" s="297"/>
-      <c r="Z1" s="297"/>
-      <c r="AA1" s="297"/>
-      <c r="AB1" s="297"/>
-      <c r="AC1" s="297"/>
-      <c r="AD1" s="297"/>
-      <c r="AE1" s="297"/>
-      <c r="AF1" s="297"/>
-      <c r="AG1" s="297"/>
-      <c r="AH1" s="297"/>
-      <c r="AI1" s="298"/>
-      <c r="AJ1" s="297"/>
-      <c r="AK1" s="297"/>
-      <c r="AL1" s="299"/>
-      <c r="AM1" s="300"/>
-      <c r="AN1" s="300"/>
+      <c r="L1" s="296"/>
+      <c r="M1" s="296"/>
+      <c r="N1" s="296"/>
+      <c r="O1" s="296"/>
+      <c r="P1" s="296"/>
+      <c r="Q1" s="296"/>
+      <c r="R1" s="296"/>
+      <c r="S1" s="296"/>
+      <c r="T1" s="296"/>
+      <c r="U1" s="296"/>
+      <c r="V1" s="296"/>
+      <c r="W1" s="296"/>
+      <c r="X1" s="296"/>
+      <c r="Y1" s="296"/>
+      <c r="Z1" s="296"/>
+      <c r="AA1" s="296"/>
+      <c r="AB1" s="296"/>
+      <c r="AC1" s="296"/>
+      <c r="AD1" s="296"/>
+      <c r="AE1" s="296"/>
+      <c r="AF1" s="296"/>
+      <c r="AG1" s="296"/>
+      <c r="AH1" s="296"/>
+      <c r="AI1" s="297"/>
+      <c r="AJ1" s="296"/>
+      <c r="AK1" s="296"/>
+      <c r="AL1" s="298"/>
+      <c r="AM1" s="299"/>
+      <c r="AN1" s="299"/>
       <c r="AO1" s="5"/>
       <c r="AR1" s="6"/>
       <c r="AS1" s="7"/>
     </row>
     <row r="2" spans="1:226" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A2" s="286">
-        <v>1</v>
-      </c>
-      <c r="B2" s="288">
+      <c r="A2" s="285">
+        <v>1</v>
+      </c>
+      <c r="B2" s="287">
         <v>2</v>
       </c>
-      <c r="C2" s="288">
-        <v>3</v>
-      </c>
-      <c r="D2" s="290" t="s">
+      <c r="C2" s="287">
+        <v>3</v>
+      </c>
+      <c r="D2" s="289" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="292" t="s">
+      <c r="E2" s="291" t="s">
         <v>61</v>
       </c>
       <c r="F2" s="8" t="s">
@@ -23366,10 +23354,10 @@
       <c r="H2" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="301" t="s">
+      <c r="I2" s="300" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="305" t="s">
+      <c r="J2" s="304" t="s">
         <v>66</v>
       </c>
       <c r="K2" s="12" t="s">
@@ -23466,18 +23454,18 @@
         <v>69</v>
       </c>
       <c r="AR2" s="6"/>
-      <c r="AV2" s="294" t="s">
+      <c r="AV2" s="293" t="s">
         <v>48</v>
       </c>
-      <c r="AW2" s="295"/>
-      <c r="AX2" s="295"/>
+      <c r="AW2" s="294"/>
+      <c r="AX2" s="294"/>
     </row>
     <row r="3" spans="1:226" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A3" s="287"/>
-      <c r="B3" s="289"/>
-      <c r="C3" s="289"/>
-      <c r="D3" s="291"/>
-      <c r="E3" s="293"/>
+      <c r="A3" s="286"/>
+      <c r="B3" s="288"/>
+      <c r="C3" s="288"/>
+      <c r="D3" s="290"/>
+      <c r="E3" s="292"/>
       <c r="F3" s="15" t="s">
         <v>74</v>
       </c>
@@ -23487,8 +23475,8 @@
       <c r="H3" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="I3" s="302"/>
-      <c r="J3" s="306"/>
+      <c r="I3" s="301"/>
+      <c r="J3" s="305"/>
       <c r="K3" s="144">
         <v>1</v>
       </c>
@@ -38334,54 +38322,54 @@
         <v>14</v>
       </c>
       <c r="J1" s="4"/>
-      <c r="K1" s="296" t="str">
+      <c r="K1" s="295" t="str">
         <f>"TPKC剩餘人力："&amp;AO59&amp;" / NK剩餘人力："&amp;AP59&amp;" /  N班人力："&amp;AO54</f>
         <v>TPKC剩餘人力：0 / NK剩餘人力：0 /  N班人力：32</v>
       </c>
-      <c r="L1" s="297"/>
-      <c r="M1" s="297"/>
-      <c r="N1" s="297"/>
-      <c r="O1" s="297"/>
-      <c r="P1" s="297"/>
-      <c r="Q1" s="297"/>
-      <c r="R1" s="297"/>
-      <c r="S1" s="297"/>
-      <c r="T1" s="297"/>
-      <c r="U1" s="297"/>
-      <c r="V1" s="297"/>
-      <c r="W1" s="297"/>
-      <c r="X1" s="297"/>
-      <c r="Y1" s="297"/>
-      <c r="Z1" s="297"/>
-      <c r="AA1" s="297"/>
-      <c r="AB1" s="297"/>
-      <c r="AC1" s="297"/>
-      <c r="AD1" s="297"/>
-      <c r="AE1" s="297"/>
-      <c r="AF1" s="297"/>
-      <c r="AG1" s="297"/>
-      <c r="AH1" s="297"/>
-      <c r="AI1" s="298"/>
-      <c r="AJ1" s="297"/>
-      <c r="AK1" s="297"/>
+      <c r="L1" s="296"/>
+      <c r="M1" s="296"/>
+      <c r="N1" s="296"/>
+      <c r="O1" s="296"/>
+      <c r="P1" s="296"/>
+      <c r="Q1" s="296"/>
+      <c r="R1" s="296"/>
+      <c r="S1" s="296"/>
+      <c r="T1" s="296"/>
+      <c r="U1" s="296"/>
+      <c r="V1" s="296"/>
+      <c r="W1" s="296"/>
+      <c r="X1" s="296"/>
+      <c r="Y1" s="296"/>
+      <c r="Z1" s="296"/>
+      <c r="AA1" s="296"/>
+      <c r="AB1" s="296"/>
+      <c r="AC1" s="296"/>
+      <c r="AD1" s="296"/>
+      <c r="AE1" s="296"/>
+      <c r="AF1" s="296"/>
+      <c r="AG1" s="296"/>
+      <c r="AH1" s="296"/>
+      <c r="AI1" s="297"/>
+      <c r="AJ1" s="296"/>
+      <c r="AK1" s="296"/>
       <c r="AL1" s="183"/>
       <c r="AO1" s="6"/>
       <c r="AP1" s="7"/>
     </row>
     <row r="2" spans="1:223" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A2" s="286">
-        <v>1</v>
-      </c>
-      <c r="B2" s="288">
+      <c r="A2" s="285">
+        <v>1</v>
+      </c>
+      <c r="B2" s="287">
         <v>2</v>
       </c>
-      <c r="C2" s="288">
-        <v>3</v>
-      </c>
-      <c r="D2" s="290" t="s">
+      <c r="C2" s="287">
+        <v>3</v>
+      </c>
+      <c r="D2" s="289" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="292" t="s">
+      <c r="E2" s="291" t="s">
         <v>105</v>
       </c>
       <c r="F2" s="8" t="s">
@@ -38393,10 +38381,10 @@
       <c r="H2" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="301" t="s">
+      <c r="I2" s="300" t="s">
         <v>109</v>
       </c>
-      <c r="J2" s="307" t="s">
+      <c r="J2" s="306" t="s">
         <v>110</v>
       </c>
       <c r="K2" s="219" t="s">
@@ -38484,18 +38472,18 @@
         <v>117</v>
       </c>
       <c r="AO2" s="6"/>
-      <c r="AS2" s="294" t="s">
+      <c r="AS2" s="293" t="s">
         <v>48</v>
       </c>
-      <c r="AT2" s="295"/>
-      <c r="AU2" s="295"/>
+      <c r="AT2" s="294"/>
+      <c r="AU2" s="294"/>
     </row>
     <row r="3" spans="1:223" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A3" s="287"/>
-      <c r="B3" s="289"/>
-      <c r="C3" s="289"/>
-      <c r="D3" s="291"/>
-      <c r="E3" s="293"/>
+      <c r="A3" s="286"/>
+      <c r="B3" s="288"/>
+      <c r="C3" s="288"/>
+      <c r="D3" s="290"/>
+      <c r="E3" s="292"/>
       <c r="F3" s="15" t="s">
         <v>118</v>
       </c>
@@ -38505,8 +38493,8 @@
       <c r="H3" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="302"/>
-      <c r="J3" s="308"/>
+      <c r="I3" s="301"/>
+      <c r="J3" s="307"/>
       <c r="K3" s="220">
         <v>1</v>
       </c>
@@ -52749,57 +52737,57 @@
         <v>9</v>
       </c>
       <c r="J1" s="4"/>
-      <c r="K1" s="296" t="str">
+      <c r="K1" s="295" t="str">
         <f>"TPKC剩餘人力："&amp;AR58&amp;" / NK剩餘人力："&amp;AS58&amp;" /  N班人力："&amp;AR53</f>
-        <v>TPKC剩餘人力：-1 / NK剩餘人力：0 /  N班人力：112</v>
-      </c>
-      <c r="L1" s="297"/>
-      <c r="M1" s="297"/>
-      <c r="N1" s="297"/>
-      <c r="O1" s="297"/>
-      <c r="P1" s="297"/>
-      <c r="Q1" s="297"/>
-      <c r="R1" s="297"/>
-      <c r="S1" s="297"/>
-      <c r="T1" s="297"/>
-      <c r="U1" s="297"/>
-      <c r="V1" s="297"/>
-      <c r="W1" s="297"/>
-      <c r="X1" s="297"/>
-      <c r="Y1" s="297"/>
-      <c r="Z1" s="297"/>
-      <c r="AA1" s="297"/>
-      <c r="AB1" s="297"/>
-      <c r="AC1" s="297"/>
-      <c r="AD1" s="297"/>
-      <c r="AE1" s="297"/>
-      <c r="AF1" s="297"/>
-      <c r="AG1" s="297"/>
-      <c r="AH1" s="297"/>
-      <c r="AI1" s="298"/>
-      <c r="AJ1" s="297"/>
-      <c r="AK1" s="297"/>
-      <c r="AL1" s="299"/>
-      <c r="AM1" s="300"/>
-      <c r="AN1" s="300"/>
+        <v>TPKC剩餘人力：-1 / NK剩餘人力：0 /  N班人力：111</v>
+      </c>
+      <c r="L1" s="296"/>
+      <c r="M1" s="296"/>
+      <c r="N1" s="296"/>
+      <c r="O1" s="296"/>
+      <c r="P1" s="296"/>
+      <c r="Q1" s="296"/>
+      <c r="R1" s="296"/>
+      <c r="S1" s="296"/>
+      <c r="T1" s="296"/>
+      <c r="U1" s="296"/>
+      <c r="V1" s="296"/>
+      <c r="W1" s="296"/>
+      <c r="X1" s="296"/>
+      <c r="Y1" s="296"/>
+      <c r="Z1" s="296"/>
+      <c r="AA1" s="296"/>
+      <c r="AB1" s="296"/>
+      <c r="AC1" s="296"/>
+      <c r="AD1" s="296"/>
+      <c r="AE1" s="296"/>
+      <c r="AF1" s="296"/>
+      <c r="AG1" s="296"/>
+      <c r="AH1" s="296"/>
+      <c r="AI1" s="297"/>
+      <c r="AJ1" s="296"/>
+      <c r="AK1" s="296"/>
+      <c r="AL1" s="298"/>
+      <c r="AM1" s="299"/>
+      <c r="AN1" s="299"/>
       <c r="AO1" s="5"/>
       <c r="AR1" s="6"/>
       <c r="AS1" s="7"/>
     </row>
     <row r="2" spans="1:226" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A2" s="286">
-        <v>1</v>
-      </c>
-      <c r="B2" s="288">
+      <c r="A2" s="285">
+        <v>1</v>
+      </c>
+      <c r="B2" s="287">
         <v>2</v>
       </c>
-      <c r="C2" s="288">
-        <v>3</v>
-      </c>
-      <c r="D2" s="290" t="s">
+      <c r="C2" s="287">
+        <v>3</v>
+      </c>
+      <c r="D2" s="289" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="292" t="s">
+      <c r="E2" s="291" t="s">
         <v>105</v>
       </c>
       <c r="F2" s="8" t="s">
@@ -52811,10 +52799,10 @@
       <c r="H2" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="301" t="s">
+      <c r="I2" s="300" t="s">
         <v>109</v>
       </c>
-      <c r="J2" s="303" t="s">
+      <c r="J2" s="302" t="s">
         <v>151</v>
       </c>
       <c r="K2" s="219" t="s">
@@ -52911,18 +52899,18 @@
         <v>113</v>
       </c>
       <c r="AR2" s="6"/>
-      <c r="AV2" s="294" t="s">
+      <c r="AV2" s="293" t="s">
         <v>48</v>
       </c>
-      <c r="AW2" s="295"/>
-      <c r="AX2" s="295"/>
+      <c r="AW2" s="294"/>
+      <c r="AX2" s="294"/>
     </row>
     <row r="3" spans="1:226" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A3" s="287"/>
-      <c r="B3" s="289"/>
-      <c r="C3" s="289"/>
-      <c r="D3" s="291"/>
-      <c r="E3" s="293"/>
+      <c r="A3" s="286"/>
+      <c r="B3" s="288"/>
+      <c r="C3" s="288"/>
+      <c r="D3" s="290"/>
+      <c r="E3" s="292"/>
       <c r="F3" s="15" t="s">
         <v>118</v>
       </c>
@@ -52932,8 +52920,8 @@
       <c r="H3" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="302"/>
-      <c r="J3" s="304"/>
+      <c r="I3" s="301"/>
+      <c r="J3" s="303"/>
       <c r="K3" s="220">
         <v>1</v>
       </c>
@@ -53055,7 +53043,7 @@
     <row r="4" spans="1:226" ht="25.5" customHeight="1">
       <c r="A4" s="23">
         <f>COUNTIF(K4:AO4,1)+COUNTIF(K4:AO4,"早")+COUNTIF(K4:AO4,"M1")+COUNTIF(K4:AO4,"T早")+COUNTIF(K4:AO4,"日")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="24">
         <f>COUNTIF(K4:AO4,2)+COUNTIF(K4:AO4,"中")+COUNTIF(K4:AO4,"M2")+COUNTIF(K4:AO4,"T中")+COUNTIF(K4:AO4,"小夜")</f>
@@ -53071,7 +53059,7 @@
       </c>
       <c r="E4" s="26">
         <f>COUNTIF(K4:AO4,"S")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="26">
         <f>COUNTIF(K4:AO4,"X")</f>
@@ -53113,8 +53101,8 @@
       <c r="Q4" s="272" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="272" t="s">
-        <v>0</v>
+      <c r="R4" s="271" t="s">
+        <v>1</v>
       </c>
       <c r="S4" s="271" t="s">
         <v>1</v>
@@ -53182,8 +53170,8 @@
       <c r="AN4" s="270" t="s">
         <v>52</v>
       </c>
-      <c r="AO4" s="285" t="s">
-        <v>36</v>
+      <c r="AO4" s="272" t="s">
+        <v>0</v>
       </c>
       <c r="AP4" s="35">
         <v>0</v>
@@ -53530,7 +53518,7 @@
     <row r="7" spans="1:226" ht="25.5" customHeight="1">
       <c r="A7" s="38">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="39">
         <f t="shared" si="3"/>
@@ -53542,7 +53530,7 @@
       </c>
       <c r="D7" s="39">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="41">
         <f t="shared" si="6"/>
@@ -53657,8 +53645,8 @@
       <c r="AN7" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="AO7" s="241" t="s">
-        <v>3</v>
+      <c r="AO7" s="30" t="s">
+        <v>36</v>
       </c>
       <c r="AP7" s="45">
         <v>0</v>
@@ -54182,7 +54170,7 @@
     <row r="10" spans="1:226" s="50" customFormat="1" ht="24" customHeight="1">
       <c r="A10" s="38">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="39">
         <f t="shared" si="3"/>
@@ -54210,7 +54198,7 @@
       </c>
       <c r="H10" s="41">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" s="42">
         <f t="shared" si="0"/>
@@ -54222,8 +54210,8 @@
       <c r="K10" s="237" t="s">
         <v>0</v>
       </c>
-      <c r="L10" s="279" t="s">
-        <v>53</v>
+      <c r="L10" s="282">
+        <v>1</v>
       </c>
       <c r="M10" s="30" t="s">
         <v>36</v>
@@ -54317,10 +54305,10 @@
       </c>
       <c r="AQ10" s="46">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR10" s="46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS10" s="134">
         <f t="shared" si="10"/>
@@ -65241,7 +65229,7 @@
       </c>
       <c r="L47" s="128" cm="2">
         <f t="array" ref="L47">SUMPRODUCT(COUNTIF(L4:L46,{"1";"M1"}))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M47" s="128" cm="2">
         <f t="array" ref="M47">SUMPRODUCT(COUNTIF(M4:M46,{"1";"M1"}))</f>
@@ -66233,7 +66221,7 @@
       </c>
       <c r="AR53" s="91" cm="1">
         <f t="array" ref="AR53">SUMPRODUCT(COUNTIF(K4:AO40,{"N";"N8"}))</f>
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AS53" s="91" cm="1">
         <f t="array" ref="AS53">SUMPRODUCT(COUNTIF(K41:AO46,{"N";"N8"}))</f>
@@ -66379,7 +66367,7 @@
       </c>
       <c r="AR54" s="92">
         <f>SUMPRODUCT(COUNTIF(K4:AO40,{"S"}))</f>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AS54" s="75">
         <f>SUMPRODUCT(COUNTIF(K41:AO46,{"S"}))</f>
@@ -66662,7 +66650,7 @@
       </c>
       <c r="AO56" s="99">
         <f t="shared" si="51"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ56" s="100" t="s">
         <v>42</v>
@@ -66691,7 +66679,7 @@
       </c>
       <c r="L57" s="24">
         <f t="shared" si="53"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M57" s="24">
         <f t="shared" ref="M57:U57" si="54">COUNTIF(M4:M46,"X")+COUNTIF(M4:M46,"Y")+COUNTIF(M4:M46,"Z")</f>
@@ -66715,7 +66703,7 @@
       </c>
       <c r="R57" s="24">
         <f t="shared" si="54"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S57" s="24">
         <f t="shared" si="54"/>
@@ -66807,7 +66795,7 @@
       </c>
       <c r="AO57" s="102">
         <f t="shared" si="53"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ57" s="100" t="s">
         <v>146</v>
@@ -66859,7 +66847,7 @@
       </c>
       <c r="R58" s="39">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S58" s="39">
         <f t="shared" si="56"/>
@@ -67256,7 +67244,7 @@
       </c>
       <c r="L61" s="113">
         <f>43-L56-L57-L58-25</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="113">
         <f t="shared" ref="M61:P61" si="60">43-M56-M57-M58-25</f>
@@ -67469,7 +67457,7 @@
       </c>
       <c r="L64" s="230" cm="1">
         <f t="array" ref="L64">SUMPRODUCT(COUNTIF(L4:L18,{"1";"M1"}))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M64" s="230" cm="1">
         <f t="array" ref="M64">SUMPRODUCT(COUNTIF(M4:M18,{"1";"M1"}))</f>
@@ -67616,87 +67604,87 @@
     <mergeCell ref="E2:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="K4:AO46">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>OR(K4=3, K4="晚",  K4="大夜")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="23" priority="2">
       <formula>OR(K4="M2", K4=2, K4="中", K4="T中", K4="小夜")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="22" priority="3">
       <formula>OR(K4="M1", K4=1, K4="早", K4="T早", K4="日")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="21" priority="4">
       <formula>OR(     SUM(COUNTIF(K4:Q4, 上班代號)) &gt; 6,     AND(COLUMN()&gt;11, OR(         AND(SUM(COUNTIF(OFFSET(K4,0,-1), 中班組)), SUM(COUNTIF(K4, 早班組), COUNTIF(K4, 晚班組))),         AND(SUM(COUNTIF(OFFSET(K4,0,-1), 早班組)), SUM(COUNTIF(K4, 晚班組)))     )) )</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K47:AO55">
-    <cfRule type="cellIs" dxfId="24" priority="202" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="202" operator="equal">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="203" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="203" operator="equal">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="204" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="204" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="205" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="205" operator="equal">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="206" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="206" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K53:AO55">
-    <cfRule type="cellIs" dxfId="19" priority="207" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="207" operator="equal">
       <formula>"T中"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP25">
-    <cfRule type="cellIs" dxfId="18" priority="210" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="210" operator="equal">
       <formula>"大夜"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="211" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="211" operator="equal">
       <formula>"晚"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="212" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="212" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="213" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="213" operator="equal">
       <formula>"小夜"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="214" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="214" operator="equal">
       <formula>"T中"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="215" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="215" operator="equal">
       <formula>"中"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="216" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="216" operator="equal">
       <formula>"M2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="217" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="217" operator="equal">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="218" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="218" operator="equal">
       <formula>"日"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="219" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="219" operator="equal">
       <formula>"T早"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="220" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="220" operator="equal">
       <formula>"早"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="221" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="221" operator="equal">
       <formula>"M1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="222" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="222" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS4:AS46">
-    <cfRule type="cellIs" dxfId="5" priority="208" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="208" operator="equal">
       <formula>-2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="209" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="209" operator="equal">
       <formula>-1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/All_2026.xlsx
+++ b/All_2026.xlsx
@@ -9,7 +9,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fetonline-my.sharepoint.com/personal/jasonh5_fareastone_com_tw/Documents/桌面/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:10000_{0B63F5BA-DE81-4C73-AF12-8D588C21A7C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:10000_{E20D8C4B-923D-4E71-950A-98D38F4EAE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{F48F8574-E72E-47A9-9FAE-C071219C9035}"/>
   </bookViews>
@@ -19351,7 +19351,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3484" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3481" uniqueCount="153">
   <si>
     <t>X</t>
   </si>
@@ -22341,30 +22341,6 @@
     <xf numFmtId="0" fontId="95" fillId="19" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="15" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -22397,6 +22373,30 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -23292,57 +23292,57 @@
         <v>10</v>
       </c>
       <c r="J1" s="4"/>
-      <c r="K1" s="295" t="str">
+      <c r="K1" s="287" t="str">
         <f>"TPKC剩餘人力："&amp;AR59&amp;" / NK剩餘人力："&amp;AS59&amp;" /  N班人力："&amp;AR53</f>
         <v>TPKC剩餘人力：0 / NK剩餘人力：0 /  N班人力：92</v>
       </c>
-      <c r="L1" s="296"/>
-      <c r="M1" s="296"/>
-      <c r="N1" s="296"/>
-      <c r="O1" s="296"/>
-      <c r="P1" s="296"/>
-      <c r="Q1" s="296"/>
-      <c r="R1" s="296"/>
-      <c r="S1" s="296"/>
-      <c r="T1" s="296"/>
-      <c r="U1" s="296"/>
-      <c r="V1" s="296"/>
-      <c r="W1" s="296"/>
-      <c r="X1" s="296"/>
-      <c r="Y1" s="296"/>
-      <c r="Z1" s="296"/>
-      <c r="AA1" s="296"/>
-      <c r="AB1" s="296"/>
-      <c r="AC1" s="296"/>
-      <c r="AD1" s="296"/>
-      <c r="AE1" s="296"/>
-      <c r="AF1" s="296"/>
-      <c r="AG1" s="296"/>
-      <c r="AH1" s="296"/>
-      <c r="AI1" s="297"/>
-      <c r="AJ1" s="296"/>
-      <c r="AK1" s="296"/>
-      <c r="AL1" s="298"/>
-      <c r="AM1" s="299"/>
-      <c r="AN1" s="299"/>
+      <c r="L1" s="288"/>
+      <c r="M1" s="288"/>
+      <c r="N1" s="288"/>
+      <c r="O1" s="288"/>
+      <c r="P1" s="288"/>
+      <c r="Q1" s="288"/>
+      <c r="R1" s="288"/>
+      <c r="S1" s="288"/>
+      <c r="T1" s="288"/>
+      <c r="U1" s="288"/>
+      <c r="V1" s="288"/>
+      <c r="W1" s="288"/>
+      <c r="X1" s="288"/>
+      <c r="Y1" s="288"/>
+      <c r="Z1" s="288"/>
+      <c r="AA1" s="288"/>
+      <c r="AB1" s="288"/>
+      <c r="AC1" s="288"/>
+      <c r="AD1" s="288"/>
+      <c r="AE1" s="288"/>
+      <c r="AF1" s="288"/>
+      <c r="AG1" s="288"/>
+      <c r="AH1" s="288"/>
+      <c r="AI1" s="289"/>
+      <c r="AJ1" s="288"/>
+      <c r="AK1" s="288"/>
+      <c r="AL1" s="290"/>
+      <c r="AM1" s="291"/>
+      <c r="AN1" s="291"/>
       <c r="AO1" s="5"/>
       <c r="AR1" s="6"/>
       <c r="AS1" s="7"/>
     </row>
     <row r="2" spans="1:226" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A2" s="285">
-        <v>1</v>
-      </c>
-      <c r="B2" s="287">
+      <c r="A2" s="296">
+        <v>1</v>
+      </c>
+      <c r="B2" s="298">
         <v>2</v>
       </c>
-      <c r="C2" s="287">
-        <v>3</v>
-      </c>
-      <c r="D2" s="289" t="s">
+      <c r="C2" s="298">
+        <v>3</v>
+      </c>
+      <c r="D2" s="300" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="291" t="s">
+      <c r="E2" s="302" t="s">
         <v>61</v>
       </c>
       <c r="F2" s="8" t="s">
@@ -23354,7 +23354,7 @@
       <c r="H2" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="300" t="s">
+      <c r="I2" s="292" t="s">
         <v>65</v>
       </c>
       <c r="J2" s="304" t="s">
@@ -23454,18 +23454,18 @@
         <v>69</v>
       </c>
       <c r="AR2" s="6"/>
-      <c r="AV2" s="293" t="s">
+      <c r="AV2" s="285" t="s">
         <v>48</v>
       </c>
-      <c r="AW2" s="294"/>
-      <c r="AX2" s="294"/>
+      <c r="AW2" s="286"/>
+      <c r="AX2" s="286"/>
     </row>
     <row r="3" spans="1:226" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A3" s="286"/>
-      <c r="B3" s="288"/>
-      <c r="C3" s="288"/>
-      <c r="D3" s="290"/>
-      <c r="E3" s="292"/>
+      <c r="A3" s="297"/>
+      <c r="B3" s="299"/>
+      <c r="C3" s="299"/>
+      <c r="D3" s="301"/>
+      <c r="E3" s="303"/>
       <c r="F3" s="15" t="s">
         <v>74</v>
       </c>
@@ -23475,7 +23475,7 @@
       <c r="H3" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="I3" s="301"/>
+      <c r="I3" s="293"/>
       <c r="J3" s="305"/>
       <c r="K3" s="144">
         <v>1</v>
@@ -38152,17 +38152,17 @@
   <autoFilter ref="AT3:AT59" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <mergeCells count="11">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
     <mergeCell ref="AV2:AX2"/>
     <mergeCell ref="K1:AH1"/>
     <mergeCell ref="AI1:AK1"/>
     <mergeCell ref="AL1:AN1"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="K4:AO46">
     <cfRule type="cellIs" dxfId="83" priority="1" operator="equal">
@@ -38322,54 +38322,54 @@
         <v>14</v>
       </c>
       <c r="J1" s="4"/>
-      <c r="K1" s="295" t="str">
+      <c r="K1" s="287" t="str">
         <f>"TPKC剩餘人力："&amp;AO59&amp;" / NK剩餘人力："&amp;AP59&amp;" /  N班人力："&amp;AO54</f>
         <v>TPKC剩餘人力：0 / NK剩餘人力：0 /  N班人力：32</v>
       </c>
-      <c r="L1" s="296"/>
-      <c r="M1" s="296"/>
-      <c r="N1" s="296"/>
-      <c r="O1" s="296"/>
-      <c r="P1" s="296"/>
-      <c r="Q1" s="296"/>
-      <c r="R1" s="296"/>
-      <c r="S1" s="296"/>
-      <c r="T1" s="296"/>
-      <c r="U1" s="296"/>
-      <c r="V1" s="296"/>
-      <c r="W1" s="296"/>
-      <c r="X1" s="296"/>
-      <c r="Y1" s="296"/>
-      <c r="Z1" s="296"/>
-      <c r="AA1" s="296"/>
-      <c r="AB1" s="296"/>
-      <c r="AC1" s="296"/>
-      <c r="AD1" s="296"/>
-      <c r="AE1" s="296"/>
-      <c r="AF1" s="296"/>
-      <c r="AG1" s="296"/>
-      <c r="AH1" s="296"/>
-      <c r="AI1" s="297"/>
-      <c r="AJ1" s="296"/>
-      <c r="AK1" s="296"/>
+      <c r="L1" s="288"/>
+      <c r="M1" s="288"/>
+      <c r="N1" s="288"/>
+      <c r="O1" s="288"/>
+      <c r="P1" s="288"/>
+      <c r="Q1" s="288"/>
+      <c r="R1" s="288"/>
+      <c r="S1" s="288"/>
+      <c r="T1" s="288"/>
+      <c r="U1" s="288"/>
+      <c r="V1" s="288"/>
+      <c r="W1" s="288"/>
+      <c r="X1" s="288"/>
+      <c r="Y1" s="288"/>
+      <c r="Z1" s="288"/>
+      <c r="AA1" s="288"/>
+      <c r="AB1" s="288"/>
+      <c r="AC1" s="288"/>
+      <c r="AD1" s="288"/>
+      <c r="AE1" s="288"/>
+      <c r="AF1" s="288"/>
+      <c r="AG1" s="288"/>
+      <c r="AH1" s="288"/>
+      <c r="AI1" s="289"/>
+      <c r="AJ1" s="288"/>
+      <c r="AK1" s="288"/>
       <c r="AL1" s="183"/>
       <c r="AO1" s="6"/>
       <c r="AP1" s="7"/>
     </row>
     <row r="2" spans="1:223" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A2" s="285">
-        <v>1</v>
-      </c>
-      <c r="B2" s="287">
+      <c r="A2" s="296">
+        <v>1</v>
+      </c>
+      <c r="B2" s="298">
         <v>2</v>
       </c>
-      <c r="C2" s="287">
-        <v>3</v>
-      </c>
-      <c r="D2" s="289" t="s">
+      <c r="C2" s="298">
+        <v>3</v>
+      </c>
+      <c r="D2" s="300" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="291" t="s">
+      <c r="E2" s="302" t="s">
         <v>105</v>
       </c>
       <c r="F2" s="8" t="s">
@@ -38381,7 +38381,7 @@
       <c r="H2" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="300" t="s">
+      <c r="I2" s="292" t="s">
         <v>109</v>
       </c>
       <c r="J2" s="306" t="s">
@@ -38472,18 +38472,18 @@
         <v>117</v>
       </c>
       <c r="AO2" s="6"/>
-      <c r="AS2" s="293" t="s">
+      <c r="AS2" s="285" t="s">
         <v>48</v>
       </c>
-      <c r="AT2" s="294"/>
-      <c r="AU2" s="294"/>
+      <c r="AT2" s="286"/>
+      <c r="AU2" s="286"/>
     </row>
     <row r="3" spans="1:223" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A3" s="286"/>
-      <c r="B3" s="288"/>
-      <c r="C3" s="288"/>
-      <c r="D3" s="290"/>
-      <c r="E3" s="292"/>
+      <c r="A3" s="297"/>
+      <c r="B3" s="299"/>
+      <c r="C3" s="299"/>
+      <c r="D3" s="301"/>
+      <c r="E3" s="303"/>
       <c r="F3" s="15" t="s">
         <v>118</v>
       </c>
@@ -38493,7 +38493,7 @@
       <c r="H3" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="301"/>
+      <c r="I3" s="293"/>
       <c r="J3" s="307"/>
       <c r="K3" s="220">
         <v>1</v>
@@ -40128,8 +40128,8 @@
       <c r="AH11" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="AI11" s="121" t="s">
-        <v>5</v>
+      <c r="AI11" s="121">
+        <v>1</v>
       </c>
       <c r="AJ11" s="30" t="s">
         <v>36</v>
@@ -52737,57 +52737,57 @@
         <v>9</v>
       </c>
       <c r="J1" s="4"/>
-      <c r="K1" s="295" t="str">
+      <c r="K1" s="287" t="str">
         <f>"TPKC剩餘人力："&amp;AR58&amp;" / NK剩餘人力："&amp;AS58&amp;" /  N班人力："&amp;AR53</f>
         <v>TPKC剩餘人力：-1 / NK剩餘人力：0 /  N班人力：111</v>
       </c>
-      <c r="L1" s="296"/>
-      <c r="M1" s="296"/>
-      <c r="N1" s="296"/>
-      <c r="O1" s="296"/>
-      <c r="P1" s="296"/>
-      <c r="Q1" s="296"/>
-      <c r="R1" s="296"/>
-      <c r="S1" s="296"/>
-      <c r="T1" s="296"/>
-      <c r="U1" s="296"/>
-      <c r="V1" s="296"/>
-      <c r="W1" s="296"/>
-      <c r="X1" s="296"/>
-      <c r="Y1" s="296"/>
-      <c r="Z1" s="296"/>
-      <c r="AA1" s="296"/>
-      <c r="AB1" s="296"/>
-      <c r="AC1" s="296"/>
-      <c r="AD1" s="296"/>
-      <c r="AE1" s="296"/>
-      <c r="AF1" s="296"/>
-      <c r="AG1" s="296"/>
-      <c r="AH1" s="296"/>
-      <c r="AI1" s="297"/>
-      <c r="AJ1" s="296"/>
-      <c r="AK1" s="296"/>
-      <c r="AL1" s="298"/>
-      <c r="AM1" s="299"/>
-      <c r="AN1" s="299"/>
+      <c r="L1" s="288"/>
+      <c r="M1" s="288"/>
+      <c r="N1" s="288"/>
+      <c r="O1" s="288"/>
+      <c r="P1" s="288"/>
+      <c r="Q1" s="288"/>
+      <c r="R1" s="288"/>
+      <c r="S1" s="288"/>
+      <c r="T1" s="288"/>
+      <c r="U1" s="288"/>
+      <c r="V1" s="288"/>
+      <c r="W1" s="288"/>
+      <c r="X1" s="288"/>
+      <c r="Y1" s="288"/>
+      <c r="Z1" s="288"/>
+      <c r="AA1" s="288"/>
+      <c r="AB1" s="288"/>
+      <c r="AC1" s="288"/>
+      <c r="AD1" s="288"/>
+      <c r="AE1" s="288"/>
+      <c r="AF1" s="288"/>
+      <c r="AG1" s="288"/>
+      <c r="AH1" s="288"/>
+      <c r="AI1" s="289"/>
+      <c r="AJ1" s="288"/>
+      <c r="AK1" s="288"/>
+      <c r="AL1" s="290"/>
+      <c r="AM1" s="291"/>
+      <c r="AN1" s="291"/>
       <c r="AO1" s="5"/>
       <c r="AR1" s="6"/>
       <c r="AS1" s="7"/>
     </row>
     <row r="2" spans="1:226" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A2" s="285">
-        <v>1</v>
-      </c>
-      <c r="B2" s="287">
+      <c r="A2" s="296">
+        <v>1</v>
+      </c>
+      <c r="B2" s="298">
         <v>2</v>
       </c>
-      <c r="C2" s="287">
-        <v>3</v>
-      </c>
-      <c r="D2" s="289" t="s">
+      <c r="C2" s="298">
+        <v>3</v>
+      </c>
+      <c r="D2" s="300" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="291" t="s">
+      <c r="E2" s="302" t="s">
         <v>105</v>
       </c>
       <c r="F2" s="8" t="s">
@@ -52799,10 +52799,10 @@
       <c r="H2" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="300" t="s">
+      <c r="I2" s="292" t="s">
         <v>109</v>
       </c>
-      <c r="J2" s="302" t="s">
+      <c r="J2" s="294" t="s">
         <v>151</v>
       </c>
       <c r="K2" s="219" t="s">
@@ -52899,18 +52899,18 @@
         <v>113</v>
       </c>
       <c r="AR2" s="6"/>
-      <c r="AV2" s="293" t="s">
+      <c r="AV2" s="285" t="s">
         <v>48</v>
       </c>
-      <c r="AW2" s="294"/>
-      <c r="AX2" s="294"/>
+      <c r="AW2" s="286"/>
+      <c r="AX2" s="286"/>
     </row>
     <row r="3" spans="1:226" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A3" s="286"/>
-      <c r="B3" s="288"/>
-      <c r="C3" s="288"/>
-      <c r="D3" s="290"/>
-      <c r="E3" s="292"/>
+      <c r="A3" s="297"/>
+      <c r="B3" s="299"/>
+      <c r="C3" s="299"/>
+      <c r="D3" s="301"/>
+      <c r="E3" s="303"/>
       <c r="F3" s="15" t="s">
         <v>118</v>
       </c>
@@ -52920,8 +52920,8 @@
       <c r="H3" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="301"/>
-      <c r="J3" s="303"/>
+      <c r="I3" s="293"/>
+      <c r="J3" s="295"/>
       <c r="K3" s="220">
         <v>1</v>
       </c>
@@ -54509,7 +54509,7 @@
     <row r="11" spans="1:226" s="50" customFormat="1" ht="25.5" customHeight="1">
       <c r="A11" s="38">
         <f>COUNTIF(K11:AO11,1)+COUNTIF(K11:AO11,"早")+COUNTIF(K11:AO11,"M1")+COUNTIF(K11:AO11,"T早")+COUNTIF(K11:AO11,"日")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B11" s="39">
         <f>COUNTIF(K11:AO11,2)+COUNTIF(K11:AO11,"中")+COUNTIF(K11:AO11,"M2")+COUNTIF(K11:AO11,"T中")+COUNTIF(K11:AO11,"小夜")</f>
@@ -54537,7 +54537,7 @@
       </c>
       <c r="H11" s="41">
         <f>COUNTIF(K11:AO11,"Z")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" s="42">
         <f t="shared" si="0"/>
@@ -54612,8 +54612,8 @@
       <c r="AF11" s="239" t="s">
         <v>0</v>
       </c>
-      <c r="AG11" s="279" t="s">
-        <v>53</v>
+      <c r="AG11" s="279">
+        <v>1</v>
       </c>
       <c r="AH11" s="238" t="s">
         <v>36</v>
@@ -54624,8 +54624,8 @@
       <c r="AJ11" s="256" t="s">
         <v>5</v>
       </c>
-      <c r="AK11" s="279" t="s">
-        <v>53</v>
+      <c r="AK11" s="279">
+        <v>1</v>
       </c>
       <c r="AL11" s="238" t="s">
         <v>52</v>
@@ -54644,14 +54644,14 @@
       </c>
       <c r="AQ11" s="46">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR11" s="46">
         <v>0</v>
       </c>
       <c r="AS11" s="134">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AT11" s="139" t="s">
         <v>126</v>
@@ -65313,7 +65313,7 @@
       </c>
       <c r="AG47" s="128" cm="2">
         <f t="array" ref="AG47">SUMPRODUCT(COUNTIF(AG4:AG46,{"1";"M1"}))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH47" s="128" cm="2">
         <f t="array" ref="AH47">SUMPRODUCT(COUNTIF(AH4:AH46,{"1";"M1"}))</f>
@@ -65329,7 +65329,7 @@
       </c>
       <c r="AK47" s="128" cm="2">
         <f t="array" ref="AK47">SUMPRODUCT(COUNTIF(AK4:AK46,{"1";"M1"}))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL47" s="128" cm="2">
         <f t="array" ref="AL47">SUMPRODUCT(COUNTIF(AL4:AL46,{"1";"M1"}))</f>
@@ -66763,7 +66763,7 @@
       </c>
       <c r="AG57" s="24">
         <f t="shared" si="53"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH57" s="24">
         <f t="shared" si="53"/>
@@ -66779,7 +66779,7 @@
       </c>
       <c r="AK57" s="24">
         <f t="shared" si="53"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL57" s="24">
         <f t="shared" si="53"/>
@@ -67328,7 +67328,7 @@
       </c>
       <c r="AG61" s="113">
         <f>43-AG56-AG57-AG58-25</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH61" s="113">
         <f t="shared" ref="AH61:AK61" si="63">43-AH56-AH57-AH58-25</f>
@@ -67344,7 +67344,7 @@
       </c>
       <c r="AK61" s="113">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL61" s="113">
         <f>43-AL56-AL57-AL58-19</f>
@@ -67541,7 +67541,7 @@
       </c>
       <c r="AG64" s="230" cm="1">
         <f t="array" ref="AG64">SUMPRODUCT(COUNTIF(AG4:AG18,{"1";"M1"}))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH64" s="230" cm="1">
         <f t="array" ref="AH64">SUMPRODUCT(COUNTIF(AH4:AH18,{"1";"M1"}))</f>
@@ -67557,7 +67557,7 @@
       </c>
       <c r="AK64" s="230" cm="1">
         <f t="array" ref="AK64">SUMPRODUCT(COUNTIF(AK4:AK18,{"1";"M1"}))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL64" s="231" cm="1">
         <f t="array" ref="AL64">SUMPRODUCT(COUNTIF(AL4:AL18,{"1";"M1"}))</f>
@@ -67591,17 +67591,17 @@
   </sheetData>
   <autoFilter ref="AT3:AT59" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells count="11">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
     <mergeCell ref="AV2:AX2"/>
     <mergeCell ref="K1:AH1"/>
     <mergeCell ref="AI1:AK1"/>
     <mergeCell ref="AL1:AN1"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="K4:AO46">
     <cfRule type="expression" dxfId="24" priority="1">

--- a/All_2026.xlsx
+++ b/All_2026.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <fileSharing readOnlyRecommended="1" userName="Jason Hsu" algorithmName="SHA-512" hashValue="5YmQLY3fiF0q8IsqV2N2AQkXFxFjJiz9KbCuAULj8unOIdcx3Zc4oUQxqi6vfsPgA5mB3FdloF2qzRjKO72h2A==" saltValue="JOpLyOm0Hd2UlBKUsb/kAA==" spinCount="100000"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -9,7 +9,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fetonline-my.sharepoint.com/personal/jasonh5_fareastone_com_tw/Documents/桌面/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:10000_{E20D8C4B-923D-4E71-950A-98D38F4EAE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:10000_{B82E93AA-D881-42CD-85D6-CC84301385B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{F48F8574-E72E-47A9-9FAE-C071219C9035}"/>
   </bookViews>
@@ -13355,6 +13355,22 @@
         </r>
       </text>
     </comment>
+    <comment ref="AD6" authorId="2" shapeId="0" xr:uid="{14B7069C-881D-4DB0-B989-4D5B05F9D885}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t xml:space="preserve">創新獎領獎
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AE6" authorId="2" shapeId="0" xr:uid="{F923D8E4-98B7-46E4-83F8-09D0D71502C3}">
       <text>
         <r>
@@ -13526,6 +13542,38 @@
         </r>
       </text>
     </comment>
+    <comment ref="AC8" authorId="2" shapeId="0" xr:uid="{EA630C50-5607-4D8F-832E-DD6F8D99E848}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t xml:space="preserve">創新獎領獎
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AD8" authorId="2" shapeId="0" xr:uid="{5036D485-D7B0-46C1-9434-48BEB60E1ADA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t xml:space="preserve">創新獎領獎
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AG8" authorId="2" shapeId="0" xr:uid="{98E7F1FE-37CF-438A-AEF4-2C4DA1C0280B}">
       <text>
         <r>
@@ -13650,21 +13698,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="L10" authorId="1" shapeId="0" xr:uid="{B4899455-2B0D-4EED-96A7-E553B68D23E8}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="11"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>過年補假
-申報加班</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="Q10" authorId="2" shapeId="0" xr:uid="{07E8260B-BBA7-4434-9493-8FA01CD1D5AA}">
       <text>
         <r>
@@ -13967,54 +14000,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG11" authorId="1" shapeId="0" xr:uid="{1E40C72F-3500-4F8A-A374-E47D006A40CD}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>過年補假</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AK11" authorId="1" shapeId="0" xr:uid="{4437E15A-8CA0-4D36-9A34-9CFA3DF696A5}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>過年補假</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="K13" authorId="2" shapeId="0" xr:uid="{4DC88E88-B65D-4818-9B4F-315E16CAD276}">
       <text>
         <r>
@@ -14049,36 +14034,6 @@
           </rPr>
           <t xml:space="preserve">請排早或中
 </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O13" authorId="1" shapeId="0" xr:uid="{358BA58B-415D-4F86-9A7B-8CA58B15C890}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="11"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>過年補假
-申報加班</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S13" authorId="1" shapeId="0" xr:uid="{1135ECD8-390A-4A63-A005-B49DB49CE365}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="11"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>過年補假
-申報加班</t>
         </r>
       </text>
     </comment>
@@ -14587,26 +14542,18 @@
         </r>
       </text>
     </comment>
-    <comment ref="AN14" authorId="1" shapeId="0" xr:uid="{4FB5C9A4-7685-4D74-804A-B65857E8A910}">
+    <comment ref="AN14" authorId="2" shapeId="0" xr:uid="{EF4F5814-520C-4084-8A63-97A5F0D4BF7C}">
       <text>
         <r>
           <rPr>
             <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>過年補假</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
+            <sz val="14"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t xml:space="preserve">孩子固定3個月長庚回診
 </t>
         </r>
       </text>
@@ -14868,30 +14815,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA16" authorId="1" shapeId="0" xr:uid="{79C2BC8A-692B-47E4-A2A9-5F36BCCB2D27}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>過年補假</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="AB16" authorId="2" shapeId="0" xr:uid="{7194780B-6A96-4F0B-B5F3-386F95A76C14}">
       <text>
         <r>
@@ -14958,30 +14881,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ16" authorId="1" shapeId="0" xr:uid="{7DC46A13-0FF4-4332-9D06-2CD5C4A08011}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>過年補假</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="AK16" authorId="2" shapeId="0" xr:uid="{831567B5-7872-42C0-B2A4-50E9C43D0604}">
       <text>
         <r>
@@ -15205,18 +15104,50 @@
         </r>
       </text>
     </comment>
-    <comment ref="M19" authorId="1" shapeId="0" xr:uid="{E1FA73C4-58CB-4EE8-9B4F-79BD8E279C2E}">
+    <comment ref="M19" authorId="2" shapeId="0" xr:uid="{A27ABE32-2B8D-40B0-AB79-85829019F598}">
       <text>
         <r>
           <rPr>
             <b/>
-            <sz val="11"/>
+            <sz val="14"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>過年補假
-申報加班</t>
+          <t>Dear Jason:</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>特休</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>17</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t xml:space="preserve">號到期
+</t>
         </r>
       </text>
     </comment>
@@ -15867,39 +15798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U24" authorId="2" shapeId="0" xr:uid="{77DA097D-CC69-4653-BA4F-842A4AA7BA8B}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <color indexed="81"/>
-            <rFont val="細明體"/>
-            <family val="3"/>
-            <charset val="136"/>
-          </rPr>
-          <t xml:space="preserve">Web Coding
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="V24" authorId="2" shapeId="0" xr:uid="{C45D3DE2-B27E-4AE0-93B9-B4269A9A7CCB}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <color indexed="81"/>
-            <rFont val="細明體"/>
-            <family val="3"/>
-            <charset val="136"/>
-          </rPr>
-          <t xml:space="preserve">Web Coding
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W24" authorId="2" shapeId="0" xr:uid="{28D282CC-E830-47C2-A27D-2C7A664E75D7}">
       <text>
         <r>
           <rPr>
@@ -16184,30 +16083,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="T27" authorId="1" shapeId="0" xr:uid="{57BE142D-ACCE-46E2-8106-5A9FE65FFC22}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>過年補假</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="X27" authorId="2" shapeId="0" xr:uid="{020C2799-705D-44E1-99BE-49C0AD5984EB}">
       <text>
         <r>
@@ -16676,22 +16551,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="M29" authorId="2" shapeId="0" xr:uid="{97003F58-8927-4256-9085-D2B766F6F4CE}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <color indexed="81"/>
-            <rFont val="細明體"/>
-            <family val="3"/>
-            <charset val="136"/>
-          </rPr>
-          <t xml:space="preserve">Web Coding
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="N29" authorId="2" shapeId="0" xr:uid="{541C4B72-0F97-4D71-A629-A9C439E52EEF}">
       <text>
         <r>
@@ -16772,22 +16631,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="U29" authorId="2" shapeId="0" xr:uid="{C3C21C03-AD06-4809-BCB5-25BB8E8ABCE3}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <color indexed="81"/>
-            <rFont val="細明體"/>
-            <family val="3"/>
-            <charset val="136"/>
-          </rPr>
-          <t xml:space="preserve">Web Coding
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="AA29" authorId="2" shapeId="0" xr:uid="{7ECF9F7A-374C-46E6-8DA6-E4FFA4F29ABB}">
       <text>
         <r>
@@ -17106,6 +16949,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="L31" authorId="1" shapeId="0" xr:uid="{BEADE5CF-8BFA-43F2-A782-4006C8992A06}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>家中有事請假</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="P31" authorId="2" shapeId="0" xr:uid="{0A1AACFC-5DA1-4C0B-A790-DE8346D4E812}">
       <text>
         <r>
@@ -17398,30 +17255,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AN33" authorId="1" shapeId="0" xr:uid="{080002F6-BC34-4F5C-A2CB-4B6896E3AB3C}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>過年補假</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="Q34" authorId="2" shapeId="0" xr:uid="{053E3461-494F-4BCE-90C7-0495AE5B8AD9}">
       <text>
         <r>
@@ -17580,30 +17413,6 @@
             <charset val="136"/>
           </rPr>
           <t>晚班"，謝謝。</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AC34" authorId="1" shapeId="0" xr:uid="{789194C9-ED87-44CF-BB0D-16A2B483DF22}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>過年補假</t>
         </r>
         <r>
           <rPr>
@@ -18016,54 +17825,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK37" authorId="1" shapeId="0" xr:uid="{782CC95F-D6A7-433A-BA96-CD48BC17E241}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>過年補假</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AO37" authorId="1" shapeId="0" xr:uid="{D2F2093E-DBD4-451F-9B44-D183B29201CB}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>過年補假</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="AA38" authorId="2" shapeId="0" xr:uid="{5B0838EA-7991-44FA-895A-991912BF50A1}">
       <text>
         <r>
@@ -18075,30 +17836,6 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Cloud Meeting
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AI38" authorId="1" shapeId="0" xr:uid="{351402B8-E873-4366-A3D0-57615F237AD0}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>過年補假</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
 </t>
         </r>
       </text>
@@ -18377,22 +18114,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="N40" authorId="2" shapeId="0" xr:uid="{C99D969B-9CAC-4394-866A-7B22E2E016B0}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <color indexed="81"/>
-            <rFont val="細明體"/>
-            <family val="3"/>
-            <charset val="136"/>
-          </rPr>
-          <t xml:space="preserve">Mobile On Job
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="O40" authorId="2" shapeId="0" xr:uid="{D8CB8D5E-01C4-4E5F-949D-D40D35365DC3}">
       <text>
         <r>
@@ -19060,6 +18781,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="P44" authorId="1" shapeId="0" xr:uid="{DC8D601B-7E4E-47C0-A577-02824C50071E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">回診
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AB44" authorId="2" shapeId="0" xr:uid="{35DB35F0-C2DC-48CA-ADA5-B5C1D8D17EC4}">
       <text>
         <r>
@@ -19072,6 +18807,20 @@
             <charset val="136"/>
           </rPr>
           <t xml:space="preserve">帶父母回診，排休或請特休
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AJ44" authorId="1" shapeId="0" xr:uid="{A211B953-7DEA-42F9-8770-A04D724A89BB}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">回診
 </t>
         </r>
       </text>
@@ -19351,7 +19100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3481" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3485" uniqueCount="153">
   <si>
     <t>X</t>
   </si>
@@ -19981,7 +19730,7 @@
     <numFmt numFmtId="165" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="166" formatCode="0_ "/>
   </numFmts>
-  <fonts count="98">
+  <fonts count="99">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -20662,8 +20411,15 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -20769,12 +20525,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -21487,7 +21237,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="308">
+  <cellXfs count="304">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -22323,23 +22073,35 @@
     <xf numFmtId="0" fontId="31" fillId="9" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="95" fillId="19" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="95" fillId="5" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="95" fillId="6" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="95" fillId="19" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="95" fillId="19" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="95" fillId="19" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="15" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -22373,30 +22135,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -23292,57 +23030,57 @@
         <v>10</v>
       </c>
       <c r="J1" s="4"/>
-      <c r="K1" s="287" t="str">
+      <c r="K1" s="291" t="str">
         <f>"TPKC剩餘人力："&amp;AR59&amp;" / NK剩餘人力："&amp;AS59&amp;" /  N班人力："&amp;AR53</f>
         <v>TPKC剩餘人力：0 / NK剩餘人力：0 /  N班人力：92</v>
       </c>
-      <c r="L1" s="288"/>
-      <c r="M1" s="288"/>
-      <c r="N1" s="288"/>
-      <c r="O1" s="288"/>
-      <c r="P1" s="288"/>
-      <c r="Q1" s="288"/>
-      <c r="R1" s="288"/>
-      <c r="S1" s="288"/>
-      <c r="T1" s="288"/>
-      <c r="U1" s="288"/>
-      <c r="V1" s="288"/>
-      <c r="W1" s="288"/>
-      <c r="X1" s="288"/>
-      <c r="Y1" s="288"/>
-      <c r="Z1" s="288"/>
-      <c r="AA1" s="288"/>
-      <c r="AB1" s="288"/>
-      <c r="AC1" s="288"/>
-      <c r="AD1" s="288"/>
-      <c r="AE1" s="288"/>
-      <c r="AF1" s="288"/>
-      <c r="AG1" s="288"/>
-      <c r="AH1" s="288"/>
-      <c r="AI1" s="289"/>
-      <c r="AJ1" s="288"/>
-      <c r="AK1" s="288"/>
-      <c r="AL1" s="290"/>
-      <c r="AM1" s="291"/>
-      <c r="AN1" s="291"/>
+      <c r="L1" s="292"/>
+      <c r="M1" s="292"/>
+      <c r="N1" s="292"/>
+      <c r="O1" s="292"/>
+      <c r="P1" s="292"/>
+      <c r="Q1" s="292"/>
+      <c r="R1" s="292"/>
+      <c r="S1" s="292"/>
+      <c r="T1" s="292"/>
+      <c r="U1" s="292"/>
+      <c r="V1" s="292"/>
+      <c r="W1" s="292"/>
+      <c r="X1" s="292"/>
+      <c r="Y1" s="292"/>
+      <c r="Z1" s="292"/>
+      <c r="AA1" s="292"/>
+      <c r="AB1" s="292"/>
+      <c r="AC1" s="292"/>
+      <c r="AD1" s="292"/>
+      <c r="AE1" s="292"/>
+      <c r="AF1" s="292"/>
+      <c r="AG1" s="292"/>
+      <c r="AH1" s="292"/>
+      <c r="AI1" s="293"/>
+      <c r="AJ1" s="292"/>
+      <c r="AK1" s="292"/>
+      <c r="AL1" s="294"/>
+      <c r="AM1" s="295"/>
+      <c r="AN1" s="295"/>
       <c r="AO1" s="5"/>
       <c r="AR1" s="6"/>
       <c r="AS1" s="7"/>
     </row>
     <row r="2" spans="1:226" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A2" s="296">
-        <v>1</v>
-      </c>
-      <c r="B2" s="298">
+      <c r="A2" s="281">
+        <v>1</v>
+      </c>
+      <c r="B2" s="283">
         <v>2</v>
       </c>
-      <c r="C2" s="298">
-        <v>3</v>
-      </c>
-      <c r="D2" s="300" t="s">
+      <c r="C2" s="283">
+        <v>3</v>
+      </c>
+      <c r="D2" s="285" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="302" t="s">
+      <c r="E2" s="287" t="s">
         <v>61</v>
       </c>
       <c r="F2" s="8" t="s">
@@ -23354,10 +23092,10 @@
       <c r="H2" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="292" t="s">
+      <c r="I2" s="296" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="304" t="s">
+      <c r="J2" s="300" t="s">
         <v>66</v>
       </c>
       <c r="K2" s="12" t="s">
@@ -23454,18 +23192,18 @@
         <v>69</v>
       </c>
       <c r="AR2" s="6"/>
-      <c r="AV2" s="285" t="s">
+      <c r="AV2" s="289" t="s">
         <v>48</v>
       </c>
-      <c r="AW2" s="286"/>
-      <c r="AX2" s="286"/>
+      <c r="AW2" s="290"/>
+      <c r="AX2" s="290"/>
     </row>
     <row r="3" spans="1:226" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A3" s="297"/>
-      <c r="B3" s="299"/>
-      <c r="C3" s="299"/>
-      <c r="D3" s="301"/>
-      <c r="E3" s="303"/>
+      <c r="A3" s="282"/>
+      <c r="B3" s="284"/>
+      <c r="C3" s="284"/>
+      <c r="D3" s="286"/>
+      <c r="E3" s="288"/>
       <c r="F3" s="15" t="s">
         <v>74</v>
       </c>
@@ -23475,8 +23213,8 @@
       <c r="H3" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="I3" s="293"/>
-      <c r="J3" s="305"/>
+      <c r="I3" s="297"/>
+      <c r="J3" s="301"/>
       <c r="K3" s="144">
         <v>1</v>
       </c>
@@ -38152,17 +37890,17 @@
   <autoFilter ref="AT3:AT59" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <mergeCells count="11">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
     <mergeCell ref="AV2:AX2"/>
     <mergeCell ref="K1:AH1"/>
     <mergeCell ref="AI1:AK1"/>
     <mergeCell ref="AL1:AN1"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="K4:AO46">
     <cfRule type="cellIs" dxfId="83" priority="1" operator="equal">
@@ -38322,54 +38060,54 @@
         <v>14</v>
       </c>
       <c r="J1" s="4"/>
-      <c r="K1" s="287" t="str">
+      <c r="K1" s="291" t="str">
         <f>"TPKC剩餘人力："&amp;AO59&amp;" / NK剩餘人力："&amp;AP59&amp;" /  N班人力："&amp;AO54</f>
         <v>TPKC剩餘人力：0 / NK剩餘人力：0 /  N班人力：32</v>
       </c>
-      <c r="L1" s="288"/>
-      <c r="M1" s="288"/>
-      <c r="N1" s="288"/>
-      <c r="O1" s="288"/>
-      <c r="P1" s="288"/>
-      <c r="Q1" s="288"/>
-      <c r="R1" s="288"/>
-      <c r="S1" s="288"/>
-      <c r="T1" s="288"/>
-      <c r="U1" s="288"/>
-      <c r="V1" s="288"/>
-      <c r="W1" s="288"/>
-      <c r="X1" s="288"/>
-      <c r="Y1" s="288"/>
-      <c r="Z1" s="288"/>
-      <c r="AA1" s="288"/>
-      <c r="AB1" s="288"/>
-      <c r="AC1" s="288"/>
-      <c r="AD1" s="288"/>
-      <c r="AE1" s="288"/>
-      <c r="AF1" s="288"/>
-      <c r="AG1" s="288"/>
-      <c r="AH1" s="288"/>
-      <c r="AI1" s="289"/>
-      <c r="AJ1" s="288"/>
-      <c r="AK1" s="288"/>
+      <c r="L1" s="292"/>
+      <c r="M1" s="292"/>
+      <c r="N1" s="292"/>
+      <c r="O1" s="292"/>
+      <c r="P1" s="292"/>
+      <c r="Q1" s="292"/>
+      <c r="R1" s="292"/>
+      <c r="S1" s="292"/>
+      <c r="T1" s="292"/>
+      <c r="U1" s="292"/>
+      <c r="V1" s="292"/>
+      <c r="W1" s="292"/>
+      <c r="X1" s="292"/>
+      <c r="Y1" s="292"/>
+      <c r="Z1" s="292"/>
+      <c r="AA1" s="292"/>
+      <c r="AB1" s="292"/>
+      <c r="AC1" s="292"/>
+      <c r="AD1" s="292"/>
+      <c r="AE1" s="292"/>
+      <c r="AF1" s="292"/>
+      <c r="AG1" s="292"/>
+      <c r="AH1" s="292"/>
+      <c r="AI1" s="293"/>
+      <c r="AJ1" s="292"/>
+      <c r="AK1" s="292"/>
       <c r="AL1" s="183"/>
       <c r="AO1" s="6"/>
       <c r="AP1" s="7"/>
     </row>
     <row r="2" spans="1:223" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A2" s="296">
-        <v>1</v>
-      </c>
-      <c r="B2" s="298">
+      <c r="A2" s="281">
+        <v>1</v>
+      </c>
+      <c r="B2" s="283">
         <v>2</v>
       </c>
-      <c r="C2" s="298">
-        <v>3</v>
-      </c>
-      <c r="D2" s="300" t="s">
+      <c r="C2" s="283">
+        <v>3</v>
+      </c>
+      <c r="D2" s="285" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="302" t="s">
+      <c r="E2" s="287" t="s">
         <v>105</v>
       </c>
       <c r="F2" s="8" t="s">
@@ -38381,10 +38119,10 @@
       <c r="H2" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="292" t="s">
+      <c r="I2" s="296" t="s">
         <v>109</v>
       </c>
-      <c r="J2" s="306" t="s">
+      <c r="J2" s="302" t="s">
         <v>110</v>
       </c>
       <c r="K2" s="219" t="s">
@@ -38472,18 +38210,18 @@
         <v>117</v>
       </c>
       <c r="AO2" s="6"/>
-      <c r="AS2" s="285" t="s">
+      <c r="AS2" s="289" t="s">
         <v>48</v>
       </c>
-      <c r="AT2" s="286"/>
-      <c r="AU2" s="286"/>
+      <c r="AT2" s="290"/>
+      <c r="AU2" s="290"/>
     </row>
     <row r="3" spans="1:223" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A3" s="297"/>
-      <c r="B3" s="299"/>
-      <c r="C3" s="299"/>
-      <c r="D3" s="301"/>
-      <c r="E3" s="303"/>
+      <c r="A3" s="282"/>
+      <c r="B3" s="284"/>
+      <c r="C3" s="284"/>
+      <c r="D3" s="286"/>
+      <c r="E3" s="288"/>
       <c r="F3" s="15" t="s">
         <v>118</v>
       </c>
@@ -38493,8 +38231,8 @@
       <c r="H3" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="293"/>
-      <c r="J3" s="307"/>
+      <c r="I3" s="297"/>
+      <c r="J3" s="303"/>
       <c r="K3" s="220">
         <v>1</v>
       </c>
@@ -39818,11 +39556,11 @@
         <v>-6</v>
       </c>
       <c r="AO10" s="46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP10" s="134">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ10" s="139" t="s">
         <v>128</v>
@@ -40148,11 +39886,11 @@
         <v>-6</v>
       </c>
       <c r="AO11" s="46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AP11" s="134">
         <f t="shared" si="10"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AQ11" s="139" t="s">
         <v>126</v>
@@ -40808,11 +40546,11 @@
         <v>-6</v>
       </c>
       <c r="AO13" s="46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AP13" s="134">
         <f t="shared" si="10"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AQ13" s="139" t="s">
         <v>126</v>
@@ -41138,11 +40876,11 @@
         <v>-6</v>
       </c>
       <c r="AO14" s="46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP14" s="134">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ14" s="139" t="s">
         <v>128</v>
@@ -41790,11 +41528,11 @@
         <v>-6</v>
       </c>
       <c r="AO16" s="46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AP16" s="134">
         <f t="shared" si="10"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AQ16" s="139" t="s">
         <v>128</v>
@@ -42429,11 +42167,11 @@
         <v>-6</v>
       </c>
       <c r="AO19" s="167">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP19" s="168">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ19" s="138" t="s">
         <v>128</v>
@@ -44643,11 +44381,11 @@
         <v>-6</v>
       </c>
       <c r="AO27" s="46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP27" s="134">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ27" s="139" t="s">
         <v>126</v>
@@ -44832,7 +44570,7 @@
       <c r="HM27" s="6"/>
       <c r="HN27" s="6"/>
     </row>
-    <row r="28" spans="1:223" s="50" customFormat="1" ht="25.35" customHeight="1">
+    <row r="28" spans="1:223" s="50" customFormat="1" ht="25.2" customHeight="1">
       <c r="A28" s="38">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -46569,11 +46307,11 @@
         <v>-6</v>
       </c>
       <c r="AO33" s="74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP33" s="127">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ33" s="140" t="s">
         <v>126</v>
@@ -47855,11 +47593,11 @@
         <v>-6</v>
       </c>
       <c r="AO37" s="46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AP37" s="134">
         <f t="shared" si="10"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AQ37" s="139" t="s">
         <v>128</v>
@@ -48177,11 +47915,11 @@
         <v>-6</v>
       </c>
       <c r="AO38" s="46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP38" s="134">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ38" s="139" t="s">
         <v>126</v>
@@ -52737,57 +52475,57 @@
         <v>9</v>
       </c>
       <c r="J1" s="4"/>
-      <c r="K1" s="287" t="str">
+      <c r="K1" s="291" t="str">
         <f>"TPKC剩餘人力："&amp;AR58&amp;" / NK剩餘人力："&amp;AS58&amp;" /  N班人力："&amp;AR53</f>
-        <v>TPKC剩餘人力：-1 / NK剩餘人力：0 /  N班人力：111</v>
-      </c>
-      <c r="L1" s="288"/>
-      <c r="M1" s="288"/>
-      <c r="N1" s="288"/>
-      <c r="O1" s="288"/>
-      <c r="P1" s="288"/>
-      <c r="Q1" s="288"/>
-      <c r="R1" s="288"/>
-      <c r="S1" s="288"/>
-      <c r="T1" s="288"/>
-      <c r="U1" s="288"/>
-      <c r="V1" s="288"/>
-      <c r="W1" s="288"/>
-      <c r="X1" s="288"/>
-      <c r="Y1" s="288"/>
-      <c r="Z1" s="288"/>
-      <c r="AA1" s="288"/>
-      <c r="AB1" s="288"/>
-      <c r="AC1" s="288"/>
-      <c r="AD1" s="288"/>
-      <c r="AE1" s="288"/>
-      <c r="AF1" s="288"/>
-      <c r="AG1" s="288"/>
-      <c r="AH1" s="288"/>
-      <c r="AI1" s="289"/>
-      <c r="AJ1" s="288"/>
-      <c r="AK1" s="288"/>
-      <c r="AL1" s="290"/>
-      <c r="AM1" s="291"/>
-      <c r="AN1" s="291"/>
+        <v>TPKC剩餘人力：1 / NK剩餘人力：0 /  N班人力：117</v>
+      </c>
+      <c r="L1" s="292"/>
+      <c r="M1" s="292"/>
+      <c r="N1" s="292"/>
+      <c r="O1" s="292"/>
+      <c r="P1" s="292"/>
+      <c r="Q1" s="292"/>
+      <c r="R1" s="292"/>
+      <c r="S1" s="292"/>
+      <c r="T1" s="292"/>
+      <c r="U1" s="292"/>
+      <c r="V1" s="292"/>
+      <c r="W1" s="292"/>
+      <c r="X1" s="292"/>
+      <c r="Y1" s="292"/>
+      <c r="Z1" s="292"/>
+      <c r="AA1" s="292"/>
+      <c r="AB1" s="292"/>
+      <c r="AC1" s="292"/>
+      <c r="AD1" s="292"/>
+      <c r="AE1" s="292"/>
+      <c r="AF1" s="292"/>
+      <c r="AG1" s="292"/>
+      <c r="AH1" s="292"/>
+      <c r="AI1" s="293"/>
+      <c r="AJ1" s="292"/>
+      <c r="AK1" s="292"/>
+      <c r="AL1" s="294"/>
+      <c r="AM1" s="295"/>
+      <c r="AN1" s="295"/>
       <c r="AO1" s="5"/>
       <c r="AR1" s="6"/>
       <c r="AS1" s="7"/>
     </row>
     <row r="2" spans="1:226" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A2" s="296">
-        <v>1</v>
-      </c>
-      <c r="B2" s="298">
+      <c r="A2" s="281">
+        <v>1</v>
+      </c>
+      <c r="B2" s="283">
         <v>2</v>
       </c>
-      <c r="C2" s="298">
-        <v>3</v>
-      </c>
-      <c r="D2" s="300" t="s">
+      <c r="C2" s="283">
+        <v>3</v>
+      </c>
+      <c r="D2" s="285" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="302" t="s">
+      <c r="E2" s="287" t="s">
         <v>105</v>
       </c>
       <c r="F2" s="8" t="s">
@@ -52799,10 +52537,10 @@
       <c r="H2" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="292" t="s">
+      <c r="I2" s="296" t="s">
         <v>109</v>
       </c>
-      <c r="J2" s="294" t="s">
+      <c r="J2" s="298" t="s">
         <v>151</v>
       </c>
       <c r="K2" s="219" t="s">
@@ -52899,18 +52637,18 @@
         <v>113</v>
       </c>
       <c r="AR2" s="6"/>
-      <c r="AV2" s="285" t="s">
+      <c r="AV2" s="289" t="s">
         <v>48</v>
       </c>
-      <c r="AW2" s="286"/>
-      <c r="AX2" s="286"/>
+      <c r="AW2" s="290"/>
+      <c r="AX2" s="290"/>
     </row>
     <row r="3" spans="1:226" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A3" s="297"/>
-      <c r="B3" s="299"/>
-      <c r="C3" s="299"/>
-      <c r="D3" s="301"/>
-      <c r="E3" s="303"/>
+      <c r="A3" s="282"/>
+      <c r="B3" s="284"/>
+      <c r="C3" s="284"/>
+      <c r="D3" s="286"/>
+      <c r="E3" s="288"/>
       <c r="F3" s="15" t="s">
         <v>118</v>
       </c>
@@ -52920,8 +52658,8 @@
       <c r="H3" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="293"/>
-      <c r="J3" s="295"/>
+      <c r="I3" s="297"/>
+      <c r="J3" s="299"/>
       <c r="K3" s="220">
         <v>1</v>
       </c>
@@ -53080,7 +52818,7 @@
       <c r="J4" s="267" t="s">
         <v>152</v>
       </c>
-      <c r="K4" s="280" t="s">
+      <c r="K4" s="279" t="s">
         <v>0</v>
       </c>
       <c r="L4" s="271" t="s">
@@ -53113,13 +52851,13 @@
       <c r="U4" s="271" t="s">
         <v>0</v>
       </c>
-      <c r="V4" s="281">
-        <v>3</v>
-      </c>
-      <c r="W4" s="281">
-        <v>3</v>
-      </c>
-      <c r="X4" s="281">
+      <c r="V4" s="280">
+        <v>3</v>
+      </c>
+      <c r="W4" s="280">
+        <v>3</v>
+      </c>
+      <c r="X4" s="280">
         <v>3</v>
       </c>
       <c r="Y4" s="270" t="s">
@@ -53131,19 +52869,19 @@
       <c r="AA4" s="270" t="s">
         <v>40</v>
       </c>
-      <c r="AB4" s="281">
-        <v>3</v>
-      </c>
-      <c r="AC4" s="281">
-        <v>3</v>
-      </c>
-      <c r="AD4" s="281">
-        <v>3</v>
-      </c>
-      <c r="AE4" s="281">
-        <v>3</v>
-      </c>
-      <c r="AF4" s="281">
+      <c r="AB4" s="280">
+        <v>3</v>
+      </c>
+      <c r="AC4" s="280">
+        <v>3</v>
+      </c>
+      <c r="AD4" s="280">
+        <v>3</v>
+      </c>
+      <c r="AE4" s="280">
+        <v>3</v>
+      </c>
+      <c r="AF4" s="280">
         <v>3</v>
       </c>
       <c r="AG4" s="271" t="s">
@@ -53155,16 +52893,16 @@
       <c r="AI4" s="271" t="s">
         <v>0</v>
       </c>
-      <c r="AJ4" s="281">
-        <v>3</v>
-      </c>
-      <c r="AK4" s="281">
-        <v>3</v>
-      </c>
-      <c r="AL4" s="281">
-        <v>3</v>
-      </c>
-      <c r="AM4" s="281">
+      <c r="AJ4" s="280">
+        <v>3</v>
+      </c>
+      <c r="AK4" s="280">
+        <v>3</v>
+      </c>
+      <c r="AL4" s="280">
+        <v>3</v>
+      </c>
+      <c r="AM4" s="280">
         <v>3</v>
       </c>
       <c r="AN4" s="270" t="s">
@@ -53356,7 +53094,7 @@
     <row r="6" spans="1:226" ht="25.5" customHeight="1">
       <c r="A6" s="38">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" s="39">
         <f t="shared" si="3"/>
@@ -53368,7 +53106,7 @@
       </c>
       <c r="D6" s="39">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" s="41">
         <f t="shared" si="6"/>
@@ -53396,8 +53134,8 @@
       <c r="K6" s="200" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="238">
-        <v>1</v>
+      <c r="L6" s="238" t="s">
+        <v>3</v>
       </c>
       <c r="M6" s="30" t="s">
         <v>36</v>
@@ -53450,7 +53188,7 @@
       <c r="AC6" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="AD6" s="238" t="s">
+      <c r="AD6" s="242" t="s">
         <v>3</v>
       </c>
       <c r="AE6" s="239" t="s">
@@ -53466,7 +53204,7 @@
         <v>3</v>
       </c>
       <c r="AI6" s="238" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="AJ6" s="238" t="s">
         <v>3</v>
@@ -53588,8 +53326,8 @@
       <c r="U7" s="238">
         <v>1</v>
       </c>
-      <c r="V7" s="238">
-        <v>1</v>
+      <c r="V7" s="30" t="s">
+        <v>36</v>
       </c>
       <c r="W7" s="234" t="s">
         <v>1</v>
@@ -53771,10 +53509,10 @@
       <c r="AB8" s="238" t="s">
         <v>3</v>
       </c>
-      <c r="AC8" s="238" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD8" s="238" t="s">
+      <c r="AC8" s="242" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD8" s="242" t="s">
         <v>3</v>
       </c>
       <c r="AE8" s="239" t="s">
@@ -54210,7 +53948,7 @@
       <c r="K10" s="237" t="s">
         <v>0</v>
       </c>
-      <c r="L10" s="282">
+      <c r="L10" s="238">
         <v>1</v>
       </c>
       <c r="M10" s="30" t="s">
@@ -54301,14 +54039,14 @@
         <v>36</v>
       </c>
       <c r="AP10" s="45">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ10" s="46">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AR10" s="46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS10" s="134">
         <f t="shared" si="10"/>
@@ -54509,7 +54247,7 @@
     <row r="11" spans="1:226" s="50" customFormat="1" ht="25.5" customHeight="1">
       <c r="A11" s="38">
         <f>COUNTIF(K11:AO11,1)+COUNTIF(K11:AO11,"早")+COUNTIF(K11:AO11,"M1")+COUNTIF(K11:AO11,"T早")+COUNTIF(K11:AO11,"日")</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B11" s="39">
         <f>COUNTIF(K11:AO11,2)+COUNTIF(K11:AO11,"中")+COUNTIF(K11:AO11,"M2")+COUNTIF(K11:AO11,"T中")+COUNTIF(K11:AO11,"小夜")</f>
@@ -54521,7 +54259,7 @@
       </c>
       <c r="D11" s="39">
         <f>COUNTIF(K11:AO11,"N")+COUNTIF(K11:AO11,"N8")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E11" s="41">
         <f>COUNTIF(K11:AO11,"S")</f>
@@ -54612,8 +54350,8 @@
       <c r="AF11" s="239" t="s">
         <v>0</v>
       </c>
-      <c r="AG11" s="279">
-        <v>1</v>
+      <c r="AG11" s="238" t="s">
+        <v>3</v>
       </c>
       <c r="AH11" s="238" t="s">
         <v>36</v>
@@ -54624,8 +54362,8 @@
       <c r="AJ11" s="256" t="s">
         <v>5</v>
       </c>
-      <c r="AK11" s="279">
-        <v>1</v>
+      <c r="AK11" s="238" t="s">
+        <v>3</v>
       </c>
       <c r="AL11" s="238" t="s">
         <v>52</v>
@@ -54640,7 +54378,7 @@
         <v>0</v>
       </c>
       <c r="AP11" s="45">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AQ11" s="46">
         <f t="shared" si="1"/>
@@ -54651,7 +54389,7 @@
       </c>
       <c r="AS11" s="134">
         <f t="shared" si="10"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AT11" s="139" t="s">
         <v>126</v>
@@ -55187,7 +54925,7 @@
     <row r="13" spans="1:226" s="50" customFormat="1" ht="28.35" customHeight="1">
       <c r="A13" s="38">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B13" s="39">
         <f t="shared" si="3"/>
@@ -55199,7 +54937,7 @@
       </c>
       <c r="D13" s="39">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E13" s="41">
         <f t="shared" si="6"/>
@@ -55236,8 +54974,8 @@
       <c r="N13" s="238">
         <v>1</v>
       </c>
-      <c r="O13" s="282">
-        <v>1</v>
+      <c r="O13" s="238" t="s">
+        <v>3</v>
       </c>
       <c r="P13" s="234" t="s">
         <v>1</v>
@@ -55248,8 +54986,8 @@
       <c r="R13" s="239" t="s">
         <v>0</v>
       </c>
-      <c r="S13" s="282">
-        <v>1</v>
+      <c r="S13" s="238" t="s">
+        <v>3</v>
       </c>
       <c r="T13" s="30" t="s">
         <v>36</v>
@@ -55318,14 +55056,14 @@
         <v>1</v>
       </c>
       <c r="AP13" s="45">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AQ13" s="46">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AR13" s="46">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS13" s="134">
         <f t="shared" si="10"/>
@@ -55542,7 +55280,7 @@
       </c>
       <c r="E14" s="41">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="41">
         <f t="shared" si="7"/>
@@ -55554,7 +55292,7 @@
       </c>
       <c r="H14" s="41">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="42">
         <f t="shared" si="0"/>
@@ -55650,18 +55388,18 @@
       <c r="AM14" s="238">
         <v>3</v>
       </c>
-      <c r="AN14" s="279" t="s">
-        <v>53</v>
+      <c r="AN14" s="234" t="s">
+        <v>1</v>
       </c>
       <c r="AO14" s="241">
         <v>2</v>
       </c>
       <c r="AP14" s="45">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ14" s="46">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR14" s="46">
         <v>0</v>
@@ -56208,7 +55946,7 @@
       </c>
       <c r="D16" s="39">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" s="41">
         <f t="shared" si="6"/>
@@ -56224,7 +55962,7 @@
       </c>
       <c r="H16" s="41">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" s="42">
         <f t="shared" si="0"/>
@@ -56281,8 +56019,8 @@
       <c r="Z16" s="238" t="s">
         <v>3</v>
       </c>
-      <c r="AA16" s="279" t="s">
-        <v>53</v>
+      <c r="AA16" s="238" t="s">
+        <v>3</v>
       </c>
       <c r="AB16" s="234" t="s">
         <v>0</v>
@@ -56308,8 +56046,8 @@
       <c r="AI16" s="238" t="s">
         <v>3</v>
       </c>
-      <c r="AJ16" s="279" t="s">
-        <v>53</v>
+      <c r="AJ16" s="238" t="s">
+        <v>3</v>
       </c>
       <c r="AK16" s="234" t="s">
         <v>1</v>
@@ -56327,11 +56065,11 @@
         <v>5</v>
       </c>
       <c r="AP16" s="45">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AQ16" s="46">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR16" s="46">
         <v>0</v>
@@ -56534,7 +56272,7 @@
     <row r="17" spans="1:226" ht="25.2" customHeight="1">
       <c r="A17" s="54">
         <f>COUNTIF(K17:AO17,1)+COUNTIF(K17:AO17,"早")+COUNTIF(K17:AO17,"M1")+COUNTIF(K17:AO17,"T早")+COUNTIF(K17:AO17,"日")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" s="55">
         <f>COUNTIF(K17:AO17,2)+COUNTIF(K17:AO17,"中")+COUNTIF(K17:AO17,"M2")+COUNTIF(K17:AO17,"T中")+COUNTIF(K17:AO17,"小夜")</f>
@@ -56546,7 +56284,7 @@
       </c>
       <c r="D17" s="55">
         <f>COUNTIF(K17:AO17,"N")+COUNTIF(K17:AO17,"N8")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="17">
         <f>COUNTIF(K17:AO17,"S")</f>
@@ -56598,8 +56336,8 @@
       <c r="S17" s="238" t="s">
         <v>0</v>
       </c>
-      <c r="T17" s="238">
-        <v>1</v>
+      <c r="T17" s="238" t="s">
+        <v>3</v>
       </c>
       <c r="U17" s="238">
         <v>1</v>
@@ -56696,7 +56434,7 @@
     <row r="18" spans="1:226" ht="25.5" customHeight="1" thickBot="1">
       <c r="A18" s="38">
         <f t="shared" ref="A18" si="12">COUNTIF(K18:AO18,1)+COUNTIF(K18:AO18,"早")+COUNTIF(K18:AO18,"M1")+COUNTIF(K18:AO18,"T早")+COUNTIF(K18:AO18,"日")</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="39">
         <f t="shared" ref="B18" si="13">COUNTIF(K18:AO18,2)+COUNTIF(K18:AO18,"中")+COUNTIF(K18:AO18,"M2")+COUNTIF(K18:AO18,"T中")+COUNTIF(K18:AO18,"小夜")</f>
@@ -56708,7 +56446,7 @@
       </c>
       <c r="D18" s="39">
         <f t="shared" ref="D18" si="15">COUNTIF(K18:AO18,"N")+COUNTIF(K18:AO18,"N8")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="41">
         <f t="shared" ref="E18" si="16">COUNTIF(K18:AO18,"S")</f>
@@ -56787,8 +56525,8 @@
       <c r="AB18" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="AC18" s="60" t="s">
-        <v>36</v>
+      <c r="AC18" s="238" t="s">
+        <v>3</v>
       </c>
       <c r="AD18" s="248" t="s">
         <v>36</v>
@@ -56858,7 +56596,7 @@
     <row r="19" spans="1:226" s="50" customFormat="1" ht="25.5" customHeight="1">
       <c r="A19" s="23">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" s="24">
         <f t="shared" si="3"/>
@@ -56874,7 +56612,7 @@
       </c>
       <c r="E19" s="26">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" s="26">
         <f t="shared" si="7"/>
@@ -56901,7 +56639,7 @@
       <c r="L19" s="270">
         <v>3</v>
       </c>
-      <c r="M19" s="282">
+      <c r="M19" s="271" t="s">
         <v>1</v>
       </c>
       <c r="N19" s="271" t="s">
@@ -56989,14 +56727,14 @@
         <v>0</v>
       </c>
       <c r="AP19" s="166">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ19" s="167">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AR19" s="167">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS19" s="168">
         <f t="shared" si="10"/>
@@ -57822,11 +57560,11 @@
     <row r="23" spans="1:226" s="50" customFormat="1" ht="25.5" customHeight="1">
       <c r="A23" s="38">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23" s="39">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" s="40">
         <f t="shared" si="4"/>
@@ -57892,8 +57630,8 @@
       <c r="U23" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="V23" s="30" t="s">
-        <v>36</v>
+      <c r="V23" s="238">
+        <v>2</v>
       </c>
       <c r="W23" s="238" t="s">
         <v>0</v>
@@ -58153,11 +57891,11 @@
     <row r="24" spans="1:226" s="50" customFormat="1" ht="25.5" customHeight="1">
       <c r="A24" s="38">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B24" s="39">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" s="40">
         <f t="shared" si="4"/>
@@ -58165,7 +57903,7 @@
       </c>
       <c r="D24" s="39">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E24" s="41">
         <f t="shared" si="6"/>
@@ -58220,20 +57958,20 @@
       <c r="T24" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="53" t="s">
-        <v>3</v>
+      <c r="U24" s="239" t="s">
+        <v>0</v>
       </c>
       <c r="V24" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="W24" s="53" t="s">
-        <v>3</v>
+      <c r="W24" s="238">
+        <v>2</v>
       </c>
       <c r="X24" s="239" t="s">
         <v>52</v>
       </c>
-      <c r="Y24" s="239" t="s">
-        <v>0</v>
+      <c r="Y24" s="238">
+        <v>1</v>
       </c>
       <c r="Z24" s="242" t="s">
         <v>3</v>
@@ -58484,7 +58222,7 @@
     <row r="25" spans="1:226" s="50" customFormat="1" ht="25.5" customHeight="1">
       <c r="A25" s="38">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B25" s="39">
         <f t="shared" si="3"/>
@@ -58496,7 +58234,7 @@
       </c>
       <c r="D25" s="39">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E25" s="41">
         <f t="shared" si="6"/>
@@ -58557,8 +58295,8 @@
       <c r="V25" s="238" t="s">
         <v>3</v>
       </c>
-      <c r="W25" s="238">
-        <v>1</v>
+      <c r="W25" s="238" t="s">
+        <v>3</v>
       </c>
       <c r="X25" s="239" t="s">
         <v>52</v>
@@ -59144,11 +58882,11 @@
     <row r="27" spans="1:226" s="50" customFormat="1" ht="25.5" customHeight="1">
       <c r="A27" s="38">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B27" s="39">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C27" s="40">
         <f t="shared" si="4"/>
@@ -59172,7 +58910,7 @@
       </c>
       <c r="H27" s="41">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="177">
         <f t="shared" si="0"/>
@@ -59208,17 +58946,17 @@
       <c r="S27" s="238">
         <v>1</v>
       </c>
-      <c r="T27" s="279" t="s">
-        <v>53</v>
+      <c r="T27" s="238">
+        <v>1</v>
       </c>
       <c r="U27" s="238" t="s">
         <v>0</v>
       </c>
       <c r="V27" s="238">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W27" s="238">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X27" s="239" t="s">
         <v>52</v>
@@ -59275,11 +59013,11 @@
         <v>0</v>
       </c>
       <c r="AP27" s="45">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ27" s="46">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR27" s="46">
         <v>0</v>
@@ -59808,7 +59546,7 @@
       </c>
       <c r="B29" s="39">
         <f>COUNTIF(K29:AO29,2)+COUNTIF(K29:AO29,"中")+COUNTIF(K29:AO29,"M2")+COUNTIF(K29:AO29,"T中")+COUNTIF(K29:AO29,"小夜")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C29" s="40">
         <f>COUNTIF(K29:AO29,3)+COUNTIF(K29:AO29,"晚")+COUNTIF(K29:AO29,"大夜")</f>
@@ -59816,11 +59554,11 @@
       </c>
       <c r="D29" s="39">
         <f>COUNTIF(K29:AO29,"N")+COUNTIF(K29:AO29,"N8")</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E29" s="41">
         <f>COUNTIF(K29:AO29,"S")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="41">
         <f>COUNTIF(K29:AO29,"X")</f>
@@ -59844,11 +59582,11 @@
       <c r="K29" s="245">
         <v>2</v>
       </c>
-      <c r="L29" s="240" t="s">
+      <c r="L29" s="238">
+        <v>2</v>
+      </c>
+      <c r="M29" s="238" t="s">
         <v>52</v>
-      </c>
-      <c r="M29" s="53" t="s">
-        <v>3</v>
       </c>
       <c r="N29" s="53" t="s">
         <v>3</v>
@@ -59871,8 +59609,8 @@
       <c r="T29" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="U29" s="53" t="s">
-        <v>3</v>
+      <c r="U29" s="234" t="s">
+        <v>1</v>
       </c>
       <c r="V29" s="238" t="s">
         <v>0</v>
@@ -60504,7 +60242,7 @@
       <c r="K31" s="245" t="s">
         <v>0</v>
       </c>
-      <c r="L31" s="246">
+      <c r="L31" s="234">
         <v>2</v>
       </c>
       <c r="M31" s="238">
@@ -60794,7 +60532,7 @@
     <row r="32" spans="1:226" s="50" customFormat="1" ht="25.5" customHeight="1">
       <c r="A32" s="38">
         <f>COUNTIF(K32:AO32,1)+COUNTIF(K32:AO32,"早")+COUNTIF(K32:AO32,"M1")+COUNTIF(K32:AO32,"T早")+COUNTIF(K32:AO32,"日")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B32" s="39">
         <f>COUNTIF(K32:AO32,2)+COUNTIF(K32:AO32,"中")+COUNTIF(K32:AO32,"M2")+COUNTIF(K32:AO32,"T中")+COUNTIF(K32:AO32,"小夜")</f>
@@ -60810,7 +60548,7 @@
       </c>
       <c r="E32" s="41">
         <f>COUNTIF(K32:AO32,"S")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="41">
         <f>COUNTIF(K32:AO32,"X")</f>
@@ -60873,7 +60611,7 @@
       <c r="X32" s="238" t="s">
         <v>52</v>
       </c>
-      <c r="Y32" s="238">
+      <c r="Y32" s="234" t="s">
         <v>1</v>
       </c>
       <c r="Z32" s="238">
@@ -61124,7 +60862,7 @@
     <row r="33" spans="1:226" s="50" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
       <c r="A33" s="69">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B33" s="70">
         <f t="shared" si="3"/>
@@ -61152,7 +60890,7 @@
       </c>
       <c r="H33" s="63">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" s="178">
         <f t="shared" si="0"/>
@@ -61248,18 +60986,18 @@
       <c r="AM33" s="251" t="s">
         <v>0</v>
       </c>
-      <c r="AN33" s="279" t="s">
-        <v>53</v>
+      <c r="AN33" s="252">
+        <v>1</v>
       </c>
       <c r="AO33" s="252">
         <v>1</v>
       </c>
       <c r="AP33" s="142">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ33" s="74">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR33" s="74">
         <v>0</v>
@@ -61454,7 +61192,7 @@
     <row r="34" spans="1:226" s="50" customFormat="1" ht="25.5" customHeight="1">
       <c r="A34" s="23">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B34" s="24">
         <f t="shared" si="3"/>
@@ -61482,7 +61220,7 @@
       </c>
       <c r="H34" s="26">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" s="176">
         <f t="shared" si="0"/>
@@ -61545,8 +61283,8 @@
       <c r="AB34" s="235" t="s">
         <v>36</v>
       </c>
-      <c r="AC34" s="283" t="s">
-        <v>53</v>
+      <c r="AC34" s="235" t="s">
+        <v>36</v>
       </c>
       <c r="AD34" s="235" t="s">
         <v>52</v>
@@ -61585,11 +61323,11 @@
         <v>40</v>
       </c>
       <c r="AP34" s="65">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ34" s="36">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR34" s="36">
         <v>0</v>
@@ -62462,7 +62200,7 @@
       </c>
       <c r="E37" s="41">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F37" s="41">
         <f t="shared" si="7"/>
@@ -62474,7 +62212,7 @@
       </c>
       <c r="H37" s="41">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I37" s="177">
         <f t="shared" si="0"/>
@@ -62544,7 +62282,7 @@
         <v>38</v>
       </c>
       <c r="AE37" s="238" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AF37" s="238" t="s">
         <v>38</v>
@@ -62561,8 +62299,8 @@
       <c r="AJ37" s="238" t="s">
         <v>0</v>
       </c>
-      <c r="AK37" s="279" t="s">
-        <v>53</v>
+      <c r="AK37" s="234" t="s">
+        <v>1</v>
       </c>
       <c r="AL37" s="238" t="s">
         <v>36</v>
@@ -62573,15 +62311,15 @@
       <c r="AN37" s="234" t="s">
         <v>0</v>
       </c>
-      <c r="AO37" s="284" t="s">
-        <v>53</v>
+      <c r="AO37" s="234" t="s">
+        <v>1</v>
       </c>
       <c r="AP37" s="45">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AQ37" s="46">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR37" s="46">
         <v>0</v>
@@ -62777,7 +62515,7 @@
     <row r="38" spans="1:226" s="50" customFormat="1" ht="24" customHeight="1">
       <c r="A38" s="38">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B38" s="39">
         <f t="shared" si="3"/>
@@ -62805,7 +62543,7 @@
       </c>
       <c r="H38" s="41">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="177">
         <f t="shared" si="0"/>
@@ -62886,8 +62624,8 @@
       <c r="AH38" s="234" t="s">
         <v>0</v>
       </c>
-      <c r="AI38" s="279" t="s">
-        <v>53</v>
+      <c r="AI38" s="238" t="s">
+        <v>36</v>
       </c>
       <c r="AJ38" s="238" t="s">
         <v>38</v>
@@ -62908,11 +62646,11 @@
         <v>52</v>
       </c>
       <c r="AP38" s="45">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ38" s="46">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR38" s="46">
         <v>0</v>
@@ -63271,11 +63009,11 @@
       </c>
       <c r="D40" s="70">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E40" s="63">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="63">
         <f t="shared" si="7"/>
@@ -63305,8 +63043,8 @@
       <c r="M40" s="182" t="s">
         <v>3</v>
       </c>
-      <c r="N40" s="182" t="s">
-        <v>3</v>
+      <c r="N40" s="234" t="s">
+        <v>1</v>
       </c>
       <c r="O40" s="182" t="s">
         <v>3</v>
@@ -64084,11 +63822,11 @@
       </c>
       <c r="D43" s="39">
         <f t="shared" si="26"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E43" s="41">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="41">
         <f t="shared" si="28"/>
@@ -64166,8 +63904,8 @@
       <c r="AC43" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="AD43" s="30" t="s">
-        <v>3</v>
+      <c r="AD43" s="234" t="s">
+        <v>1</v>
       </c>
       <c r="AE43" s="30" t="s">
         <v>54</v>
@@ -64235,11 +63973,11 @@
       </c>
       <c r="D44" s="39">
         <f t="shared" si="26"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E44" s="41">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F44" s="41">
         <f t="shared" si="28"/>
@@ -64275,8 +64013,8 @@
       <c r="O44" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="30" t="s">
-        <v>3</v>
+      <c r="P44" s="234" t="s">
+        <v>1</v>
       </c>
       <c r="Q44" s="44" t="s">
         <v>52</v>
@@ -64335,8 +64073,8 @@
       <c r="AI44" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="AJ44" s="30" t="s">
-        <v>3</v>
+      <c r="AJ44" s="234" t="s">
+        <v>1</v>
       </c>
       <c r="AK44" s="30" t="s">
         <v>0</v>
@@ -65229,11 +64967,11 @@
       </c>
       <c r="L47" s="128" cm="2">
         <f t="array" ref="L47">SUMPRODUCT(COUNTIF(L4:L46,{"1";"M1"}))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M47" s="128" cm="2">
         <f t="array" ref="M47">SUMPRODUCT(COUNTIF(M4:M46,{"1";"M1"}))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N47" s="128" cm="2">
         <f t="array" ref="N47">SUMPRODUCT(COUNTIF(N4:N46,{"1";"M1"}))</f>
@@ -65241,7 +64979,7 @@
       </c>
       <c r="O47" s="128" cm="2">
         <f t="array" ref="O47">SUMPRODUCT(COUNTIF(O4:O46,{"1";"M1"}))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P47" s="128" cm="2">
         <f t="array" ref="P47">SUMPRODUCT(COUNTIF(P4:P46,{"1";"M1"}))</f>
@@ -65257,7 +64995,7 @@
       </c>
       <c r="S47" s="128" cm="2">
         <f t="array" ref="S47">SUMPRODUCT(COUNTIF(S4:S46,{"1";"M1"}))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T47" s="128" cm="2">
         <f t="array" ref="T47">SUMPRODUCT(COUNTIF(T4:T46,{"1";"M1"}))</f>
@@ -65313,7 +65051,7 @@
       </c>
       <c r="AG47" s="128" cm="2">
         <f t="array" ref="AG47">SUMPRODUCT(COUNTIF(AG4:AG46,{"1";"M1"}))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH47" s="128" cm="2">
         <f t="array" ref="AH47">SUMPRODUCT(COUNTIF(AH4:AH46,{"1";"M1"}))</f>
@@ -65329,7 +65067,7 @@
       </c>
       <c r="AK47" s="128" cm="2">
         <f t="array" ref="AK47">SUMPRODUCT(COUNTIF(AK4:AK46,{"1";"M1"}))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL47" s="128" cm="2">
         <f t="array" ref="AL47">SUMPRODUCT(COUNTIF(AL4:AL46,{"1";"M1"}))</f>
@@ -65341,7 +65079,7 @@
       </c>
       <c r="AN47" s="128" cm="2">
         <f t="array" ref="AN47">SUMPRODUCT(COUNTIF(AN4:AN46,{"1";"M1"}))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO47" s="128" cm="2">
         <f t="array" ref="AO47">SUMPRODUCT(COUNTIF(AO4:AO46,{"1";"M1"}))</f>
@@ -65368,7 +65106,7 @@
       </c>
       <c r="L48" s="129" cm="2">
         <f t="array" ref="L48">SUMPRODUCT(COUNTIF(L4:L46,{"2";"M2"}))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M48" s="129" cm="2">
         <f t="array" ref="M48">SUMPRODUCT(COUNTIF(M4:M46,{"2";"M2"}))</f>
@@ -66221,11 +65959,11 @@
       </c>
       <c r="AR53" s="91" cm="1">
         <f t="array" ref="AR53">SUMPRODUCT(COUNTIF(K4:AO40,{"N";"N8"}))</f>
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="AS53" s="91" cm="1">
         <f t="array" ref="AS53">SUMPRODUCT(COUNTIF(K41:AO46,{"N";"N8"}))</f>
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:47" s="77" customFormat="1" ht="18" customHeight="1">
@@ -66367,11 +66105,11 @@
       </c>
       <c r="AR54" s="92">
         <f>SUMPRODUCT(COUNTIF(K4:AO40,{"S"}))</f>
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="AS54" s="75">
         <f>SUMPRODUCT(COUNTIF(K41:AO46,{"S"}))</f>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:47" s="77" customFormat="1" ht="18" customHeight="1" thickBot="1">
@@ -66534,23 +66272,23 @@
       </c>
       <c r="L56" s="96">
         <f t="shared" si="51"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M56" s="96">
         <f t="shared" ref="M56:U56" si="52">COUNTIF(M4:M46,"N")+COUNTIF(M4:M46,"N8")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N56" s="96">
         <f t="shared" si="52"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O56" s="96">
         <f t="shared" si="52"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P56" s="96">
         <f t="shared" si="52"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q56" s="96">
         <f t="shared" si="52"/>
@@ -66562,15 +66300,15 @@
       </c>
       <c r="S56" s="96">
         <f t="shared" si="52"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T56" s="96">
         <f t="shared" si="52"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U56" s="96">
         <f t="shared" si="52"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V56" s="96">
         <f t="shared" si="51"/>
@@ -66594,7 +66332,7 @@
       </c>
       <c r="AA56" s="96">
         <f t="shared" si="51"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB56" s="96">
         <f t="shared" si="51"/>
@@ -66602,11 +66340,11 @@
       </c>
       <c r="AC56" s="96">
         <f t="shared" si="51"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD56" s="96">
         <f t="shared" si="51"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE56" s="96">
         <f t="shared" si="51"/>
@@ -66618,7 +66356,7 @@
       </c>
       <c r="AG56" s="96">
         <f t="shared" si="51"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH56" s="96">
         <f t="shared" si="51"/>
@@ -66626,7 +66364,7 @@
       </c>
       <c r="AI56" s="96">
         <f t="shared" si="51"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ56" s="96">
         <f t="shared" si="51"/>
@@ -66634,7 +66372,7 @@
       </c>
       <c r="AK56" s="96">
         <f t="shared" si="51"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL56" s="96">
         <f t="shared" si="51"/>
@@ -66657,7 +66395,7 @@
       </c>
       <c r="AR56" s="101">
         <f>SUM(AP4:AP40)</f>
-        <v>-16</v>
+        <v>-1</v>
       </c>
       <c r="AS56" s="75">
         <v>0</v>
@@ -66679,11 +66417,11 @@
       </c>
       <c r="L57" s="24">
         <f t="shared" si="53"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M57" s="24">
         <f t="shared" ref="M57:U57" si="54">COUNTIF(M4:M46,"X")+COUNTIF(M4:M46,"Y")+COUNTIF(M4:M46,"Z")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N57" s="24">
         <f t="shared" si="54"/>
@@ -66711,11 +66449,11 @@
       </c>
       <c r="T57" s="24">
         <f t="shared" si="54"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U57" s="24">
         <f t="shared" si="54"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V57" s="24">
         <f t="shared" si="53"/>
@@ -66731,7 +66469,7 @@
       </c>
       <c r="Y57" s="24">
         <f>COUNTIF(Y4:Y46,"X")+COUNTIF(Y4:Y46,"Y")+COUNTIF(Y4:Y46,"Z")</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z57" s="24">
         <f t="shared" si="53"/>
@@ -66739,7 +66477,7 @@
       </c>
       <c r="AA57" s="24">
         <f t="shared" si="53"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB57" s="24">
         <f t="shared" si="53"/>
@@ -66747,7 +66485,7 @@
       </c>
       <c r="AC57" s="24">
         <f t="shared" si="53"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD57" s="24">
         <f t="shared" si="53"/>
@@ -66771,15 +66509,15 @@
       </c>
       <c r="AI57" s="24">
         <f t="shared" si="53"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ57" s="24">
         <f t="shared" si="53"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK57" s="24">
         <f t="shared" si="53"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL57" s="24">
         <f t="shared" si="53"/>
@@ -66791,11 +66529,11 @@
       </c>
       <c r="AN57" s="24">
         <f t="shared" si="53"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO57" s="102">
         <f t="shared" si="53"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ57" s="100" t="s">
         <v>146</v>
@@ -66827,11 +66565,11 @@
       </c>
       <c r="M58" s="39">
         <f t="shared" ref="M58:U58" si="56">COUNTIF(M4:M46,"S")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N58" s="39">
         <f t="shared" si="56"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O58" s="39">
         <f t="shared" si="56"/>
@@ -66839,7 +66577,7 @@
       </c>
       <c r="P58" s="39">
         <f t="shared" si="56"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q58" s="39">
         <f t="shared" si="56"/>
@@ -66859,7 +66597,7 @@
       </c>
       <c r="U58" s="39">
         <f t="shared" si="56"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V58" s="39">
         <f t="shared" si="55"/>
@@ -66875,7 +66613,7 @@
       </c>
       <c r="Y58" s="39">
         <f>COUNTIF(Y4:Y46,"S")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z58" s="39">
         <f t="shared" si="55"/>
@@ -66895,7 +66633,7 @@
       </c>
       <c r="AD58" s="39">
         <f t="shared" si="55"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE58" s="39">
         <f t="shared" si="55"/>
@@ -66919,11 +66657,11 @@
       </c>
       <c r="AJ58" s="39">
         <f t="shared" si="55"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK58" s="39">
         <f t="shared" si="55"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL58" s="39">
         <f t="shared" si="55"/>
@@ -66935,18 +66673,18 @@
       </c>
       <c r="AN58" s="39">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO58" s="83">
         <f t="shared" si="55"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ58" s="107" t="s">
         <v>46</v>
       </c>
       <c r="AR58" s="105">
         <f>AR49-AR50-AR52-AR53-AR54-AR55+AR56+AR57-AR51</f>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AS58" s="105">
         <f>AS49-AS50-AS52-AS53-AS54-AS55+AS56+AS57-AS51</f>
@@ -67248,7 +66986,7 @@
       </c>
       <c r="M61" s="113">
         <f t="shared" ref="M61:P61" si="60">43-M56-M57-M58-25</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61" s="113">
         <f t="shared" si="60"/>
@@ -67256,7 +66994,7 @@
       </c>
       <c r="O61" s="113">
         <f t="shared" si="60"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P61" s="113">
         <f t="shared" si="60"/>
@@ -67272,7 +67010,7 @@
       </c>
       <c r="S61" s="113">
         <f>43-S56-S57-S58-25</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T61" s="113">
         <f t="shared" ref="T61:W61" si="61">43-T56-T57-T58-25</f>
@@ -67328,7 +67066,7 @@
       </c>
       <c r="AG61" s="113">
         <f>43-AG56-AG57-AG58-25</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH61" s="113">
         <f t="shared" ref="AH61:AK61" si="63">43-AH56-AH57-AH58-25</f>
@@ -67344,7 +67082,7 @@
       </c>
       <c r="AK61" s="113">
         <f t="shared" si="63"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL61" s="113">
         <f>43-AL56-AL57-AL58-19</f>
@@ -67356,7 +67094,7 @@
       </c>
       <c r="AN61" s="113">
         <f t="shared" ref="AN61" si="64">43-AN56-AN57-AN58-25</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO61" s="113">
         <f t="shared" ref="AO61" si="65">43-AO56-AO57-AO58-25</f>
@@ -67457,7 +67195,7 @@
       </c>
       <c r="L64" s="230" cm="1">
         <f t="array" ref="L64">SUMPRODUCT(COUNTIF(L4:L18,{"1";"M1"}))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M64" s="230" cm="1">
         <f t="array" ref="M64">SUMPRODUCT(COUNTIF(M4:M18,{"1";"M1"}))</f>
@@ -67469,7 +67207,7 @@
       </c>
       <c r="O64" s="230" cm="1">
         <f t="array" ref="O64">SUMPRODUCT(COUNTIF(O4:O18,{"1";"M1"}))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P64" s="230" cm="1">
         <f t="array" ref="P64">SUMPRODUCT(COUNTIF(P4:P18,{"1";"M1"}))</f>
@@ -67485,11 +67223,11 @@
       </c>
       <c r="S64" s="230" cm="1">
         <f t="array" ref="S64">SUMPRODUCT(COUNTIF(S4:S18,{"1";"M1"}))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T64" s="230" cm="1">
         <f t="array" ref="T64">SUMPRODUCT(COUNTIF(T4:T18,{"1";"M1"}))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U64" s="230" cm="1">
         <f t="array" ref="U64">SUMPRODUCT(COUNTIF(U4:U18,{"1";"M1"}))</f>
@@ -67497,7 +67235,7 @@
       </c>
       <c r="V64" s="230" cm="1">
         <f t="array" ref="V64">SUMPRODUCT(COUNTIF(V4:V18,{"1";"M1"}))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W64" s="230" cm="1">
         <f t="array" ref="W64">SUMPRODUCT(COUNTIF(W4:W18,{"1";"M1"}))</f>
@@ -67541,7 +67279,7 @@
       </c>
       <c r="AG64" s="230" cm="1">
         <f t="array" ref="AG64">SUMPRODUCT(COUNTIF(AG4:AG18,{"1";"M1"}))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH64" s="230" cm="1">
         <f t="array" ref="AH64">SUMPRODUCT(COUNTIF(AH4:AH18,{"1";"M1"}))</f>
@@ -67557,7 +67295,7 @@
       </c>
       <c r="AK64" s="230" cm="1">
         <f t="array" ref="AK64">SUMPRODUCT(COUNTIF(AK4:AK18,{"1";"M1"}))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL64" s="231" cm="1">
         <f t="array" ref="AL64">SUMPRODUCT(COUNTIF(AL4:AL18,{"1";"M1"}))</f>
@@ -67591,17 +67329,17 @@
   </sheetData>
   <autoFilter ref="AT3:AT59" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells count="11">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
     <mergeCell ref="AV2:AX2"/>
     <mergeCell ref="K1:AH1"/>
     <mergeCell ref="AI1:AK1"/>
     <mergeCell ref="AL1:AN1"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="K4:AO46">
     <cfRule type="expression" dxfId="24" priority="1">

--- a/All_2026.xlsx
+++ b/All_2026.xlsx
@@ -9,7 +9,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fetonline-my.sharepoint.com/personal/jasonh5_fareastone_com_tw/Documents/桌面/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:10000_{B82E93AA-D881-42CD-85D6-CC84301385B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:10000_{FAF4707B-73D7-4EF3-9D3E-57A59CBFC05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{F48F8574-E72E-47A9-9FAE-C071219C9035}"/>
   </bookViews>
@@ -13229,43 +13229,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="P6" authorId="2" shapeId="0" xr:uid="{B4A201F7-5459-497F-8F98-FFE2D80A19E3}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <color indexed="81"/>
-            <rFont val="細明體"/>
-            <family val="3"/>
-            <charset val="136"/>
-          </rPr>
-          <t>若班表允許</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>,</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <color indexed="81"/>
-            <rFont val="細明體"/>
-            <family val="3"/>
-            <charset val="136"/>
-          </rPr>
-          <t xml:space="preserve">請排早班，謝謝
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="R6" authorId="2" shapeId="0" xr:uid="{21DF065E-F892-46F9-A510-7214F997504D}">
       <text>
         <r>
@@ -13644,43 +13607,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y9" authorId="2" shapeId="0" xr:uid="{D95A0D26-6C1F-43FE-8F2A-428BD95796C9}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <color indexed="81"/>
-            <rFont val="細明體"/>
-            <family val="3"/>
-            <charset val="136"/>
-          </rPr>
-          <t>與大</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>D</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <color indexed="81"/>
-            <rFont val="細明體"/>
-            <family val="3"/>
-            <charset val="136"/>
-          </rPr>
-          <t xml:space="preserve">換
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="J10" authorId="2" shapeId="0" xr:uid="{040105F4-B00B-4D2C-970C-E265C0635791}">
       <text>
         <r>
@@ -16083,7 +16009,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X27" authorId="2" shapeId="0" xr:uid="{020C2799-705D-44E1-99BE-49C0AD5984EB}">
+    <comment ref="Y27" authorId="2" shapeId="0" xr:uid="{772EB5D2-FD92-4161-9036-AAC539C6DD0E}">
       <text>
         <r>
           <rPr>
@@ -18114,7 +18040,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O40" authorId="2" shapeId="0" xr:uid="{D8CB8D5E-01C4-4E5F-949D-D40D35365DC3}">
+    <comment ref="N40" authorId="2" shapeId="0" xr:uid="{153CD12A-5211-47F3-B6C2-2176D67F3E3D}">
       <text>
         <r>
           <rPr>
@@ -19100,7 +19026,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3485" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3482" uniqueCount="153">
   <si>
     <t>X</t>
   </si>
@@ -22156,6 +22082,31 @@
   <dxfs count="84">
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <color rgb="FFFF0000"/>
@@ -22282,31 +22233,6 @@
           <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -52477,7 +52403,7 @@
       <c r="J1" s="4"/>
       <c r="K1" s="291" t="str">
         <f>"TPKC剩餘人力："&amp;AR58&amp;" / NK剩餘人力："&amp;AS58&amp;" /  N班人力："&amp;AR53</f>
-        <v>TPKC剩餘人力：1 / NK剩餘人力：0 /  N班人力：117</v>
+        <v>TPKC剩餘人力：3 / NK剩餘人力：0 /  N班人力：114</v>
       </c>
       <c r="L1" s="292"/>
       <c r="M1" s="292"/>
@@ -53094,7 +53020,7 @@
     <row r="6" spans="1:226" ht="25.5" customHeight="1">
       <c r="A6" s="38">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="39">
         <f t="shared" si="3"/>
@@ -53106,7 +53032,7 @@
       </c>
       <c r="D6" s="39">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="41">
         <f t="shared" si="6"/>
@@ -53146,8 +53072,8 @@
       <c r="O6" s="234" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="238" t="s">
-        <v>3</v>
+      <c r="P6" s="30" t="s">
+        <v>36</v>
       </c>
       <c r="Q6" s="259">
         <v>1</v>
@@ -53569,7 +53495,7 @@
     <row r="9" spans="1:226" s="50" customFormat="1" ht="24.75" customHeight="1">
       <c r="A9" s="38">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="39">
         <f t="shared" si="3"/>
@@ -53585,7 +53511,7 @@
       </c>
       <c r="E9" s="41">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="41">
         <f t="shared" si="7"/>
@@ -53621,8 +53547,8 @@
       <c r="O9" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="P9" s="30" t="s">
-        <v>36</v>
+      <c r="P9" s="234" t="s">
+        <v>1</v>
       </c>
       <c r="Q9" s="239" t="s">
         <v>52</v>
@@ -53645,11 +53571,11 @@
       <c r="W9" s="234" t="s">
         <v>52</v>
       </c>
-      <c r="X9" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y9" s="239" t="s">
-        <v>0</v>
+      <c r="X9" s="239" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="30">
+        <v>1</v>
       </c>
       <c r="Z9" s="259">
         <v>1</v>
@@ -55671,8 +55597,8 @@
       <c r="W15" s="238" t="s">
         <v>3</v>
       </c>
-      <c r="X15" s="238">
-        <v>1</v>
+      <c r="X15" s="30" t="s">
+        <v>36</v>
       </c>
       <c r="Y15" s="238" t="s">
         <v>0</v>
@@ -55977,8 +55903,8 @@
       <c r="L16" s="246" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="256" t="s">
-        <v>5</v>
+      <c r="M16" s="259">
+        <v>1</v>
       </c>
       <c r="N16" s="30" t="s">
         <v>36</v>
@@ -58958,11 +58884,11 @@
       <c r="W27" s="238">
         <v>1</v>
       </c>
-      <c r="X27" s="239" t="s">
+      <c r="X27" s="238">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="239" t="s">
         <v>52</v>
-      </c>
-      <c r="Y27" s="238">
-        <v>1</v>
       </c>
       <c r="Z27" s="238">
         <v>1</v>
@@ -62997,7 +62923,7 @@
     <row r="40" spans="1:226" ht="25.5" customHeight="1" thickBot="1">
       <c r="A40" s="69">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B40" s="70">
         <f t="shared" si="3"/>
@@ -63009,7 +62935,7 @@
       </c>
       <c r="D40" s="70">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E40" s="63">
         <f t="shared" si="6"/>
@@ -63043,14 +62969,14 @@
       <c r="M40" s="182" t="s">
         <v>3</v>
       </c>
-      <c r="N40" s="234" t="s">
-        <v>1</v>
-      </c>
-      <c r="O40" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="P40" s="182" t="s">
-        <v>3</v>
+      <c r="N40" s="182">
+        <v>1</v>
+      </c>
+      <c r="O40" s="234" t="s">
+        <v>1</v>
+      </c>
+      <c r="P40" s="182">
+        <v>1</v>
       </c>
       <c r="Q40" s="249" t="s">
         <v>52</v>
@@ -64975,7 +64901,7 @@
       </c>
       <c r="N47" s="128" cm="2">
         <f t="array" ref="N47">SUMPRODUCT(COUNTIF(N4:N46,{"1";"M1"}))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O47" s="128" cm="2">
         <f t="array" ref="O47">SUMPRODUCT(COUNTIF(O4:O46,{"1";"M1"}))</f>
@@ -64983,7 +64909,7 @@
       </c>
       <c r="P47" s="128" cm="2">
         <f t="array" ref="P47">SUMPRODUCT(COUNTIF(P4:P46,{"1";"M1"}))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q47" s="128" cm="2">
         <f t="array" ref="Q47">SUMPRODUCT(COUNTIF(Q4:Q46,{"1";"M1"}))</f>
@@ -65959,7 +65885,7 @@
       </c>
       <c r="AR53" s="91" cm="1">
         <f t="array" ref="AR53">SUMPRODUCT(COUNTIF(K4:AO40,{"N";"N8"}))</f>
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="AS53" s="91" cm="1">
         <f t="array" ref="AS53">SUMPRODUCT(COUNTIF(K41:AO46,{"N";"N8"}))</f>
@@ -66105,7 +66031,7 @@
       </c>
       <c r="AR54" s="92">
         <f>SUMPRODUCT(COUNTIF(K4:AO40,{"S"}))</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AS54" s="75">
         <f>SUMPRODUCT(COUNTIF(K41:AO46,{"S"}))</f>
@@ -66284,11 +66210,11 @@
       </c>
       <c r="O56" s="96">
         <f t="shared" si="52"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P56" s="96">
         <f t="shared" si="52"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q56" s="96">
         <f t="shared" si="52"/>
@@ -66569,15 +66495,15 @@
       </c>
       <c r="N58" s="39">
         <f t="shared" si="56"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O58" s="39">
         <f t="shared" si="56"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P58" s="39">
         <f t="shared" si="56"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q58" s="39">
         <f t="shared" si="56"/>
@@ -66684,7 +66610,7 @@
       </c>
       <c r="AR58" s="105">
         <f>AR49-AR50-AR52-AR53-AR54-AR55+AR56+AR57-AR51</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS58" s="105">
         <f>AS49-AS50-AS52-AS53-AS54-AS55+AS56+AS57-AS51</f>
@@ -66990,7 +66916,7 @@
       </c>
       <c r="N61" s="113">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" s="113">
         <f t="shared" si="60"/>
@@ -66998,7 +66924,7 @@
       </c>
       <c r="P61" s="113">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q61" s="113">
         <f>43-Q56-Q57-Q58-19</f>
@@ -67243,11 +67169,11 @@
       </c>
       <c r="X64" s="231" cm="1">
         <f t="array" ref="X64">SUMPRODUCT(COUNTIF(X4:X18,{"1";"M1"}))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y64" s="231" cm="1">
         <f t="array" ref="Y64">SUMPRODUCT(COUNTIF(Y4:Y18,{"1";"M1"}))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z64" s="230" cm="1">
         <f t="array" ref="Z64">SUMPRODUCT(COUNTIF(Z4:Z18,{"1";"M1"}))</f>
@@ -67342,87 +67268,87 @@
     <mergeCell ref="E2:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="K4:AO46">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>OR(K4=3, K4="晚",  K4="大夜")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>OR(K4="M2", K4=2, K4="中", K4="T中", K4="小夜")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>OR(K4="M1", K4=1, K4="早", K4="T早", K4="日")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="4">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>OR(     SUM(COUNTIF(K4:Q4, 上班代號)) &gt; 6,     AND(COLUMN()&gt;11, OR(         AND(SUM(COUNTIF(OFFSET(K4,0,-1), 中班組)), SUM(COUNTIF(K4, 早班組), COUNTIF(K4, 晚班組))),         AND(SUM(COUNTIF(OFFSET(K4,0,-1), 早班組)), SUM(COUNTIF(K4, 晚班組)))     )) )</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K47:AO55">
-    <cfRule type="cellIs" dxfId="20" priority="202" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="202" operator="equal">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="203" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="203" operator="equal">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="204" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="204" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="205" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="205" operator="equal">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="206" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="206" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K53:AO55">
-    <cfRule type="cellIs" dxfId="15" priority="207" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="207" operator="equal">
       <formula>"T中"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP25">
-    <cfRule type="cellIs" dxfId="14" priority="210" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="210" operator="equal">
       <formula>"大夜"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="211" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="211" operator="equal">
       <formula>"晚"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="212" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="212" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="213" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="213" operator="equal">
       <formula>"小夜"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="214" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="214" operator="equal">
       <formula>"T中"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="215" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="215" operator="equal">
       <formula>"中"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="216" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="216" operator="equal">
       <formula>"M2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="217" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="217" operator="equal">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="218" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="218" operator="equal">
       <formula>"日"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="219" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="219" operator="equal">
       <formula>"T早"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="220" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="220" operator="equal">
       <formula>"早"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="221" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="221" operator="equal">
       <formula>"M1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="222" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="222" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS4:AS46">
-    <cfRule type="cellIs" dxfId="1" priority="208" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="208" operator="equal">
       <formula>-2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="209" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="209" operator="equal">
       <formula>-1</formula>
     </cfRule>
   </conditionalFormatting>
